--- a/14_Options_Derivatives/instances/benchmark_adversarial_skew.xlsx
+++ b/14_Options_Derivatives/instances/benchmark_adversarial_skew.xlsx
@@ -9,17 +9,25 @@
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Assumptions" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="European Pricer" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Implied Vol" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="Greeks" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="Vol Surface" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="Portfolio" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="Scenario P&amp;L" sheetId="8" state="visible" r:id="rId10"/>
-    <sheet name="Checks" sheetId="9" state="visible" r:id="rId11"/>
-    <sheet name="Sources" sheetId="10" state="visible" r:id="rId12"/>
-    <sheet name="RefreshLog" sheetId="11" state="visible" r:id="rId13"/>
+    <sheet name="Institutional Surface" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Challenge Log" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Lineage Map" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Assumptions" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="European Pricer" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Implied Vol" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Greeks" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Vol Surface" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="Portfolio" sheetId="10" state="visible" r:id="rId12"/>
+    <sheet name="Scenario P&amp;L" sheetId="11" state="visible" r:id="rId13"/>
+    <sheet name="Checks" sheetId="12" state="visible" r:id="rId14"/>
+    <sheet name="Sources" sheetId="13" state="visible" r:id="rId15"/>
+    <sheet name="RefreshLog" sheetId="14" state="visible" r:id="rId16"/>
   </sheets>
+  <definedNames>
+    <definedName function="false" hidden="false" name="FS_DOMAIN" vbProcedure="false">'Institutional Surface'!$C$5</definedName>
+    <definedName function="false" hidden="false" name="FS_MATURITY" vbProcedure="false">'Institutional Surface'!$C$6</definedName>
+    <definedName function="false" hidden="false" name="FS_MODEL_ID" vbProcedure="false">'Institutional Surface'!$C$4</definedName>
+  </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
@@ -30,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="250">
   <si>
     <t xml:space="preserve">[UNDERLYING] — Options &amp; Derivatives Model</t>
   </si>
@@ -104,6 +112,312 @@
     <t xml:space="preserve">PASS / REVIEW / FAIL must remain visible</t>
   </si>
   <si>
+    <t xml:space="preserve">Options &amp; Derivatives — Institutional Decision Surface</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Model ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Domain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Options &amp; Derivatives</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Declared maturity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canonical builder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tools/builders/build_options_release.py</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Decision arena</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trading desk, market making, independent risk and model validation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Committee artifact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">volatility and Greeks risk pack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operating cadence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">intraday desk; daily risk and margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Key decision outputs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Requirement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evidence / location</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fair value and implied volatility</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OPEN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">surface and skew</t>
+  </si>
+  <si>
+    <t xml:space="preserve">portfolio Greeks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">base, downside and break-even outputs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">liquidity / funding requirement and binding constraint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insider questions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What surface convention drives the hedge?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Where is the wing marked by model, not market?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Which Greeks are unstable near expiry?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Which assumption is owner-approved versus modeler judgement?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What fails first and who must act?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scenario families</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spot jump</t>
+  </si>
+  <si>
+    <t xml:space="preserve">parallel and localized vol shock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">skew twist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data freshness / source failure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">combined severe-but-plausible downside</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primary diligence documents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">confirmations and master agreements</t>
+  </si>
+  <si>
+    <t xml:space="preserve">exchange specifications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">volatility and market-data policy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">approved model card and assumption register</t>
+  </si>
+  <si>
+    <t xml:space="preserve">independent validation and challenge record</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Challenge tests</t>
+  </si>
+  <si>
+    <t xml:space="preserve">put-call parity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">price bounds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">surface calendar and butterfly arbitrage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">source-to-model lineage is reproducible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">units, signs, dates and legal definitions reconcile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Known failure modes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">marking off mid in illiquid wings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">interpolating through arbitrage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">using sticky-strike when sticky-delta is required</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stale vintage presented as current</t>
+  </si>
+  <si>
+    <t xml:space="preserve">decision output disconnected from a binding constraint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regulatory / methodological anchors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scope</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applicability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Review note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Federal Reserve SR 26-2 Model Risk Management</t>
+  </si>
+  <si>
+    <t xml:space="preserve">governance, validation, change control, monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.federalreserve.gov/supervisionreg/srletters/SR2602.htm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Map explicitly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Basel MAR21 Sensitivities-Based Method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">market-risk factors and aggregation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.bis.org/basel_framework/chapter/MAR/21.htm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CFTC Uncleared Swap Margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">initial and variation margin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.cftc.gov/LawRegulation/FederalRegister/FinalRules/2015-32320.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Independent Challenge, Override and Closure Log</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reviewer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Challenge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owner response</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evidence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Impact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Closure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source, Transformation, Ownership and Refresh Map</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source class</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cadence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System / provider</t>
+  </si>
+  <si>
+    <t xml:space="preserve">As-of</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Downstream</t>
+  </si>
+  <si>
+    <t xml:space="preserve">spot / forwards / rates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">intraday</t>
+  </si>
+  <si>
+    <t xml:space="preserve">timestamp and market hierarchy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TO MAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">volatility surface</t>
+  </si>
+  <si>
+    <t xml:space="preserve">intraday/daily</t>
+  </si>
+  <si>
+    <t xml:space="preserve">arbitrage and stale-point controls</t>
+  </si>
+  <si>
+    <t xml:space="preserve">model governance evidence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">per release</t>
+  </si>
+  <si>
+    <t xml:space="preserve">version, reviewer, sign-off and change log</t>
+  </si>
+  <si>
+    <t xml:space="preserve">decision-use snapshot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">per decision</t>
+  </si>
+  <si>
+    <t xml:space="preserve">immutable as-of date and source receipt</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pricing and Risk Assumptions</t>
   </si>
   <si>
@@ -188,9 +502,6 @@
     <t xml:space="preserve">Formula role</t>
   </si>
   <si>
-    <t xml:space="preserve">Control</t>
-  </si>
-  <si>
     <t xml:space="preserve">d1</t>
   </si>
   <si>
@@ -371,9 +682,6 @@
     <t xml:space="preserve">Check</t>
   </si>
   <si>
-    <t xml:space="preserve">Status</t>
-  </si>
-  <si>
     <t xml:space="preserve">Put-call parity</t>
   </si>
   <si>
@@ -401,9 +709,6 @@
     <t xml:space="preserve">Source URL or document</t>
   </si>
   <si>
-    <t xml:space="preserve">As-of</t>
-  </si>
-  <si>
     <t xml:space="preserve">Notes / transformation</t>
   </si>
   <si>
@@ -456,9 +761,6 @@
   </si>
   <si>
     <t xml:space="preserve">Refresh Log</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Date</t>
   </si>
   <si>
     <t xml:space="preserve">Trigger</t>
@@ -504,7 +806,7 @@
     <numFmt numFmtId="172" formatCode="\$#,##0.0;[RED]&quot;($&quot;#,##0.0\);\-"/>
     <numFmt numFmtId="173" formatCode="0.0%;[RED]\(0.0%\);\-"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -582,6 +884,29 @@
       <charset val="1"/>
     </font>
     <font>
+      <b val="true"/>
+      <sz val="15"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Cambria"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <name val="Cambria"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Cambria"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color rgb="FF008000"/>
       <name val="Arial"/>
@@ -589,7 +914,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -599,7 +924,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1F4E78"/>
-        <bgColor rgb="FF003366"/>
+        <bgColor rgb="FF17365D"/>
       </patternFill>
     </fill>
     <fill>
@@ -614,8 +939,20 @@
         <bgColor rgb="FFFCE4D6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF17365D"/>
+        <bgColor rgb="FF333333"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9EAF7"/>
+        <bgColor rgb="FFE2F0D9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -629,6 +966,15 @@
       <top/>
       <bottom style="thin">
         <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFB7B7B7"/>
       </bottom>
       <diagonal/>
     </border>
@@ -667,7 +1013,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="46">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -708,6 +1054,30 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -720,7 +1090,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -728,7 +1098,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -736,7 +1106,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -748,7 +1118,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -760,11 +1130,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -796,15 +1166,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="172" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -881,11 +1251,11 @@
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFFFF2CC"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFD9EAF7"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FFB7B7B7"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -910,7 +1280,7 @@
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF666699"/>
       <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF17365D"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF111827"/>
       <rgbColor rgb="FF333300"/>
@@ -1244,6 +1614,601 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="B2:M10"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="5" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="8" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="16"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B2" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B4" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>199</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="H4" s="16" t="s">
+        <v>202</v>
+      </c>
+      <c r="I4" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="J4" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="K4" s="16" t="s">
+        <v>176</v>
+      </c>
+      <c r="L4" s="16" t="s">
+        <v>203</v>
+      </c>
+      <c r="M4" s="16" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="D5" s="36" t="n">
+        <v>10</v>
+      </c>
+      <c r="E5" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="F5" s="36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G5" s="22" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H5" s="31" t="n">
+        <f aca="false">IF($C5="Call",Assumptions!$E$5*EXP(-Assumptions!$E$9*F5)*NORMSDIST((LN(Assumptions!$E$5/E5)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G5^2)*F5)/(G5*SQRT(F5)))-E5*EXP(-Assumptions!$E$8*F5)*NORMSDIST(((LN(Assumptions!$E$5/E5)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G5^2)*F5)/(G5*SQRT(F5)))-G5*SQRT(F5)),E5*EXP(-Assumptions!$E$8*F5)*NORMSDIST(-(((LN(Assumptions!$E$5/E5)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G5^2)*F5)/(G5*SQRT(F5)))-G5*SQRT(F5)))-Assumptions!$E$5*EXP(-Assumptions!$E$9*F5)*NORMSDIST(-((LN(Assumptions!$E$5/E5)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G5^2)*F5)/(G5*SQRT(F5)))))</f>
+        <v>0.21045244961855</v>
+      </c>
+      <c r="I5" s="1" t="n">
+        <f aca="false">IF($C5="Call",EXP(-Assumptions!$E$9*F5)*NORMSDIST((LN(Assumptions!$E$5/E5)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G5^2)*F5)/(G5*SQRT(F5))),EXP(-Assumptions!$E$9*F5)*(NORMSDIST((LN(Assumptions!$E$5/E5)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G5^2)*F5)/(G5*SQRT(F5)))-1))*D5</f>
+        <v>0.431086690644158</v>
+      </c>
+      <c r="J5" s="1" t="n">
+        <f aca="false">EXP(-Assumptions!$E$9*F5)*(EXP(-(((LN(Assumptions!$E$5/E5)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G5^2)*F5)/(G5*SQRT(F5)))^2)/2)/SQRT(2*PI()))/(Assumptions!$E$5*G5*SQRT(F5))*D5</f>
+        <v>0.0718680647335041</v>
+      </c>
+      <c r="K5" s="1" t="n">
+        <f aca="false">Assumptions!$E$5*EXP(-Assumptions!$E$9*F5)*(EXP(-(((LN(Assumptions!$E$5/E5)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G5^2)*F5)/(G5*SQRT(F5)))^2)/2)/SQRT(2*PI()))*SQRT(F5)*D5</f>
+        <v>46.5705059473107</v>
+      </c>
+      <c r="L5" s="1" t="n">
+        <f aca="false">-Assumptions!$E$5*EXP(-Assumptions!$E$9*F5)*(EXP(-(((LN(Assumptions!$E$5/E5)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G5^2)*F5)/(G5*SQRT(F5)))^2)/2)/SQRT(2*PI()))*G5/(2*SQRT(F5))*D5</f>
+        <v>-11.6426264868277</v>
+      </c>
+      <c r="M5" s="37" t="n">
+        <f aca="false">H5*D5*Assumptions!$E$12</f>
+        <v>210.45244961855</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="D6" s="36" t="n">
+        <v>10</v>
+      </c>
+      <c r="E6" s="17" t="n">
+        <v>90</v>
+      </c>
+      <c r="F6" s="36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G6" s="22" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H6" s="31" t="n">
+        <f aca="false">IF($C6="Call",Assumptions!$E$5*EXP(-Assumptions!$E$9*F6)*NORMSDIST((LN(Assumptions!$E$5/E6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G6^2)*F6)/(G6*SQRT(F6)))-E6*EXP(-Assumptions!$E$8*F6)*NORMSDIST(((LN(Assumptions!$E$5/E6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G6^2)*F6)/(G6*SQRT(F6)))-G6*SQRT(F6)),E6*EXP(-Assumptions!$E$8*F6)*NORMSDIST(-(((LN(Assumptions!$E$5/E6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G6^2)*F6)/(G6*SQRT(F6)))-G6*SQRT(F6)))-Assumptions!$E$5*EXP(-Assumptions!$E$9*F6)*NORMSDIST(-((LN(Assumptions!$E$5/E6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G6^2)*F6)/(G6*SQRT(F6)))))</f>
+        <v>18.4100145080232</v>
+      </c>
+      <c r="I6" s="1" t="n">
+        <f aca="false">IF($C6="Call",EXP(-Assumptions!$E$9*F6)*NORMSDIST((LN(Assumptions!$E$5/E6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G6^2)*F6)/(G6*SQRT(F6))),EXP(-Assumptions!$E$9*F6)*(NORMSDIST((LN(Assumptions!$E$5/E6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G6^2)*F6)/(G6*SQRT(F6)))-1))*D6</f>
+        <v>-8.11526585455463</v>
+      </c>
+      <c r="J6" s="1" t="n">
+        <f aca="false">EXP(-Assumptions!$E$9*F6)*(EXP(-(((LN(Assumptions!$E$5/E6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G6^2)*F6)/(G6*SQRT(F6)))^2)/2)/SQRT(2*PI()))/(Assumptions!$E$5*G6*SQRT(F6))*D6</f>
+        <v>0.173547126473767</v>
+      </c>
+      <c r="K6" s="1" t="n">
+        <f aca="false">Assumptions!$E$5*EXP(-Assumptions!$E$9*F6)*(EXP(-(((LN(Assumptions!$E$5/E6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G6^2)*F6)/(G6*SQRT(F6)))^2)/2)/SQRT(2*PI()))*SQRT(F6)*D6</f>
+        <v>134.950245546001</v>
+      </c>
+      <c r="L6" s="1" t="n">
+        <f aca="false">-Assumptions!$E$5*EXP(-Assumptions!$E$9*F6)*(EXP(-(((LN(Assumptions!$E$5/E6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G6^2)*F6)/(G6*SQRT(F6)))^2)/2)/SQRT(2*PI()))*G6/(2*SQRT(F6))*D6</f>
+        <v>-40.4850736638003</v>
+      </c>
+      <c r="M6" s="37" t="n">
+        <f aca="false">H6*D6*Assumptions!$E$12</f>
+        <v>18410.0145080232</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="D7" s="36" t="n">
+        <v>-5</v>
+      </c>
+      <c r="E7" s="17" t="n">
+        <v>110</v>
+      </c>
+      <c r="F7" s="36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G7" s="22" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H7" s="31" t="n">
+        <f aca="false">IF($C7="Call",Assumptions!$E$5*EXP(-Assumptions!$E$9*F7)*NORMSDIST((LN(Assumptions!$E$5/E7)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G7^2)*F7)/(G7*SQRT(F7)))-E7*EXP(-Assumptions!$E$8*F7)*NORMSDIST(((LN(Assumptions!$E$5/E7)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G7^2)*F7)/(G7*SQRT(F7)))-G7*SQRT(F7)),E7*EXP(-Assumptions!$E$8*F7)*NORMSDIST(-(((LN(Assumptions!$E$5/E7)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G7^2)*F7)/(G7*SQRT(F7)))-G7*SQRT(F7)))-Assumptions!$E$5*EXP(-Assumptions!$E$9*F7)*NORMSDIST(-((LN(Assumptions!$E$5/E7)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G7^2)*F7)/(G7*SQRT(F7)))))</f>
+        <v>0.036099946946677</v>
+      </c>
+      <c r="I7" s="1" t="n">
+        <f aca="false">IF($C7="Call",EXP(-Assumptions!$E$9*F7)*NORMSDIST((LN(Assumptions!$E$5/E7)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G7^2)*F7)/(G7*SQRT(F7))),EXP(-Assumptions!$E$9*F7)*(NORMSDIST((LN(Assumptions!$E$5/E7)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G7^2)*F7)/(G7*SQRT(F7)))-1))*D7</f>
+        <v>-0.0462532932434724</v>
+      </c>
+      <c r="J7" s="1" t="n">
+        <f aca="false">EXP(-Assumptions!$E$9*F7)*(EXP(-(((LN(Assumptions!$E$5/E7)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G7^2)*F7)/(G7*SQRT(F7)))^2)/2)/SQRT(2*PI()))/(Assumptions!$E$5*G7*SQRT(F7))*D7</f>
+        <v>-0.0101820891599</v>
+      </c>
+      <c r="K7" s="1" t="n">
+        <f aca="false">Assumptions!$E$5*EXP(-Assumptions!$E$9*F7)*(EXP(-(((LN(Assumptions!$E$5/E7)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G7^2)*F7)/(G7*SQRT(F7)))^2)/2)/SQRT(2*PI()))*SQRT(F7)*D7</f>
+        <v>-6.33407402459057</v>
+      </c>
+      <c r="L7" s="1" t="n">
+        <f aca="false">-Assumptions!$E$5*EXP(-Assumptions!$E$9*F7)*(EXP(-(((LN(Assumptions!$E$5/E7)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G7^2)*F7)/(G7*SQRT(F7)))^2)/2)/SQRT(2*PI()))*G7/(2*SQRT(F7))*D7</f>
+        <v>1.52017776590174</v>
+      </c>
+      <c r="M7" s="37" t="n">
+        <f aca="false">H7*D7*Assumptions!$E$12</f>
+        <v>-18.0499734733385</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="D8" s="36" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" s="17" t="n">
+        <v>105</v>
+      </c>
+      <c r="F8" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="22" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H8" s="31" t="n">
+        <f aca="false">IF($C8="Call",Assumptions!$E$5*EXP(-Assumptions!$E$9*F8)*NORMSDIST((LN(Assumptions!$E$5/E8)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G8^2)*F8)/(G8*SQRT(F8)))-E8*EXP(-Assumptions!$E$8*F8)*NORMSDIST(((LN(Assumptions!$E$5/E8)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G8^2)*F8)/(G8*SQRT(F8)))-G8*SQRT(F8)),E8*EXP(-Assumptions!$E$8*F8)*NORMSDIST(-(((LN(Assumptions!$E$5/E8)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G8^2)*F8)/(G8*SQRT(F8)))-G8*SQRT(F8)))-Assumptions!$E$5*EXP(-Assumptions!$E$9*F8)*NORMSDIST(-((LN(Assumptions!$E$5/E8)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G8^2)*F8)/(G8*SQRT(F8)))))</f>
+        <v>0.990491653278344</v>
+      </c>
+      <c r="I8" s="1" t="n">
+        <f aca="false">IF($C8="Call",EXP(-Assumptions!$E$9*F8)*NORMSDIST((LN(Assumptions!$E$5/E8)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G8^2)*F8)/(G8*SQRT(F8))),EXP(-Assumptions!$E$9*F8)*(NORMSDIST((LN(Assumptions!$E$5/E8)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G8^2)*F8)/(G8*SQRT(F8)))-1))*D8</f>
+        <v>0.46475023181471</v>
+      </c>
+      <c r="J8" s="1" t="n">
+        <f aca="false">EXP(-Assumptions!$E$9*F8)*(EXP(-(((LN(Assumptions!$E$5/E8)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G8^2)*F8)/(G8*SQRT(F8)))^2)/2)/SQRT(2*PI()))/(Assumptions!$E$5*G8*SQRT(F8))*D8</f>
+        <v>0.0401144108343275</v>
+      </c>
+      <c r="K8" s="1" t="n">
+        <f aca="false">Assumptions!$E$5*EXP(-Assumptions!$E$9*F8)*(EXP(-(((LN(Assumptions!$E$5/E8)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G8^2)*F8)/(G8*SQRT(F8)))^2)/2)/SQRT(2*PI()))*SQRT(F8)*D8</f>
+        <v>56.1473385565915</v>
+      </c>
+      <c r="L8" s="1" t="n">
+        <f aca="false">-Assumptions!$E$5*EXP(-Assumptions!$E$9*F8)*(EXP(-(((LN(Assumptions!$E$5/E8)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G8^2)*F8)/(G8*SQRT(F8)))^2)/2)/SQRT(2*PI()))*G8/(2*SQRT(F8))*D8</f>
+        <v>-7.57989070513985</v>
+      </c>
+      <c r="M8" s="37" t="n">
+        <f aca="false">H8*D8*Assumptions!$E$12</f>
+        <v>396.196661311338</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="38" t="s">
+        <v>209</v>
+      </c>
+      <c r="C10" s="38"/>
+      <c r="D10" s="38"/>
+      <c r="E10" s="38"/>
+      <c r="F10" s="38"/>
+      <c r="G10" s="38"/>
+      <c r="H10" s="38"/>
+      <c r="I10" s="39" t="n">
+        <f aca="false">SUM(I5:I8)</f>
+        <v>-7.26568222533924</v>
+      </c>
+      <c r="J10" s="39" t="n">
+        <f aca="false">SUM(J5:J8)</f>
+        <v>0.275347512881698</v>
+      </c>
+      <c r="K10" s="39" t="n">
+        <f aca="false">SUM(K5:K8)</f>
+        <v>231.334016025313</v>
+      </c>
+      <c r="L10" s="39" t="n">
+        <f aca="false">SUM(L5:L8)</f>
+        <v>-58.1874130898661</v>
+      </c>
+      <c r="M10" s="40" t="n">
+        <f aca="false">SUM(M5:M8)</f>
+        <v>18998.6136454798</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:M2"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="B2:H9"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="1" width="14"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B2" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B4" s="16" t="s">
+        <v>211</v>
+      </c>
+      <c r="C4" s="41" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="D4" s="41" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E4" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="41" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G4" s="41" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="42" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="C5" s="37" t="n">
+        <f aca="false">Portfolio!$I$10*(Assumptions!$E$5*$B5)+0.5*Portfolio!$J$10*(Assumptions!$E$5*$B5)^2+Portfolio!$K$10*C$4</f>
+        <v>110.040452577928</v>
+      </c>
+      <c r="D5" s="37" t="n">
+        <f aca="false">Portfolio!$I$10*(Assumptions!$E$5*$B5)+0.5*Portfolio!$J$10*(Assumptions!$E$5*$B5)^2+Portfolio!$K$10*D$4</f>
+        <v>121.607153379194</v>
+      </c>
+      <c r="E5" s="37" t="n">
+        <f aca="false">Portfolio!$I$10*(Assumptions!$E$5*$B5)+0.5*Portfolio!$J$10*(Assumptions!$E$5*$B5)^2+Portfolio!$K$10*E$4</f>
+        <v>133.17385418046</v>
+      </c>
+      <c r="F5" s="37" t="n">
+        <f aca="false">Portfolio!$I$10*(Assumptions!$E$5*$B5)+0.5*Portfolio!$J$10*(Assumptions!$E$5*$B5)^2+Portfolio!$K$10*F$4</f>
+        <v>144.740554981725</v>
+      </c>
+      <c r="G5" s="37" t="n">
+        <f aca="false">Portfolio!$I$10*(Assumptions!$E$5*$B5)+0.5*Portfolio!$J$10*(Assumptions!$E$5*$B5)^2+Portfolio!$K$10*G$4</f>
+        <v>156.307255782991</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="42" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="C6" s="37" t="n">
+        <f aca="false">Portfolio!$I$10*(Assumptions!$E$5*$B6)+0.5*Portfolio!$J$10*(Assumptions!$E$5*$B6)^2+Portfolio!$K$10*C$4</f>
+        <v>36.3165179538049</v>
+      </c>
+      <c r="D6" s="37" t="n">
+        <f aca="false">Portfolio!$I$10*(Assumptions!$E$5*$B6)+0.5*Portfolio!$J$10*(Assumptions!$E$5*$B6)^2+Portfolio!$K$10*D$4</f>
+        <v>47.8832187550705</v>
+      </c>
+      <c r="E6" s="37" t="n">
+        <f aca="false">Portfolio!$I$10*(Assumptions!$E$5*$B6)+0.5*Portfolio!$J$10*(Assumptions!$E$5*$B6)^2+Portfolio!$K$10*E$4</f>
+        <v>59.4499195563361</v>
+      </c>
+      <c r="F6" s="37" t="n">
+        <f aca="false">Portfolio!$I$10*(Assumptions!$E$5*$B6)+0.5*Portfolio!$J$10*(Assumptions!$E$5*$B6)^2+Portfolio!$K$10*F$4</f>
+        <v>71.0166203576018</v>
+      </c>
+      <c r="G6" s="37" t="n">
+        <f aca="false">Portfolio!$I$10*(Assumptions!$E$5*$B6)+0.5*Portfolio!$J$10*(Assumptions!$E$5*$B6)^2+Portfolio!$K$10*G$4</f>
+        <v>82.5833211588674</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="42" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="37" t="n">
+        <f aca="false">Portfolio!$I$10*(Assumptions!$E$5*$B7)+0.5*Portfolio!$J$10*(Assumptions!$E$5*$B7)^2+Portfolio!$K$10*C$4</f>
+        <v>-23.1334016025313</v>
+      </c>
+      <c r="D7" s="37" t="n">
+        <f aca="false">Portfolio!$I$10*(Assumptions!$E$5*$B7)+0.5*Portfolio!$J$10*(Assumptions!$E$5*$B7)^2+Portfolio!$K$10*D$4</f>
+        <v>-11.5667008012656</v>
+      </c>
+      <c r="E7" s="37" t="n">
+        <f aca="false">Portfolio!$I$10*(Assumptions!$E$5*$B7)+0.5*Portfolio!$J$10*(Assumptions!$E$5*$B7)^2+Portfolio!$K$10*E$4</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="37" t="n">
+        <f aca="false">Portfolio!$I$10*(Assumptions!$E$5*$B7)+0.5*Portfolio!$J$10*(Assumptions!$E$5*$B7)^2+Portfolio!$K$10*F$4</f>
+        <v>11.5667008012656</v>
+      </c>
+      <c r="G7" s="37" t="n">
+        <f aca="false">Portfolio!$I$10*(Assumptions!$E$5*$B7)+0.5*Portfolio!$J$10*(Assumptions!$E$5*$B7)^2+Portfolio!$K$10*G$4</f>
+        <v>23.1334016025313</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="42" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C8" s="37" t="n">
+        <f aca="false">Portfolio!$I$10*(Assumptions!$E$5*$B8)+0.5*Portfolio!$J$10*(Assumptions!$E$5*$B8)^2+Portfolio!$K$10*C$4</f>
+        <v>-68.3093060910802</v>
+      </c>
+      <c r="D8" s="37" t="n">
+        <f aca="false">Portfolio!$I$10*(Assumptions!$E$5*$B8)+0.5*Portfolio!$J$10*(Assumptions!$E$5*$B8)^2+Portfolio!$K$10*D$4</f>
+        <v>-56.7426052898145</v>
+      </c>
+      <c r="E8" s="37" t="n">
+        <f aca="false">Portfolio!$I$10*(Assumptions!$E$5*$B8)+0.5*Portfolio!$J$10*(Assumptions!$E$5*$B8)^2+Portfolio!$K$10*E$4</f>
+        <v>-45.1759044885489</v>
+      </c>
+      <c r="F8" s="37" t="n">
+        <f aca="false">Portfolio!$I$10*(Assumptions!$E$5*$B8)+0.5*Portfolio!$J$10*(Assumptions!$E$5*$B8)^2+Portfolio!$K$10*F$4</f>
+        <v>-33.6092036872833</v>
+      </c>
+      <c r="G8" s="37" t="n">
+        <f aca="false">Portfolio!$I$10*(Assumptions!$E$5*$B8)+0.5*Portfolio!$J$10*(Assumptions!$E$5*$B8)^2+Portfolio!$K$10*G$4</f>
+        <v>-22.0425028860176</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="42" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C9" s="37" t="n">
+        <f aca="false">Portfolio!$I$10*(Assumptions!$E$5*$B9)+0.5*Portfolio!$J$10*(Assumptions!$E$5*$B9)^2+Portfolio!$K$10*C$4</f>
+        <v>-99.2111955118418</v>
+      </c>
+      <c r="D9" s="37" t="n">
+        <f aca="false">Portfolio!$I$10*(Assumptions!$E$5*$B9)+0.5*Portfolio!$J$10*(Assumptions!$E$5*$B9)^2+Portfolio!$K$10*D$4</f>
+        <v>-87.6444947105762</v>
+      </c>
+      <c r="E9" s="37" t="n">
+        <f aca="false">Portfolio!$I$10*(Assumptions!$E$5*$B9)+0.5*Portfolio!$J$10*(Assumptions!$E$5*$B9)^2+Portfolio!$K$10*E$4</f>
+        <v>-76.0777939093105</v>
+      </c>
+      <c r="F9" s="37" t="n">
+        <f aca="false">Portfolio!$I$10*(Assumptions!$E$5*$B9)+0.5*Portfolio!$J$10*(Assumptions!$E$5*$B9)^2+Portfolio!$K$10*F$4</f>
+        <v>-64.5110931080449</v>
+      </c>
+      <c r="G9" s="37" t="n">
+        <f aca="false">Portfolio!$I$10*(Assumptions!$E$5*$B9)+0.5*Portfolio!$J$10*(Assumptions!$E$5*$B9)^2+Portfolio!$K$10*G$4</f>
+        <v>-52.9443923067793</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:H2"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C5:G9">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFFCE4D6"/>
+        <color rgb="FFFFF2CC"/>
+        <color rgb="FFE2F0D9"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="B2:C10"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B2" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C2" s="2"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B4" s="16" t="s">
+        <v>213</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="C5" s="1" t="str">
+        <f aca="false">IF(ABS('European Pricer'!C13)&lt;0.000001,"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C6" s="1" t="str">
+        <f aca="false">IF('Implied Vol'!E17&lt;0.0001,"PASS","REVIEW")</f>
+        <v>REVIEW</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C7" s="1" t="str">
+        <f aca="false">IF(AND(Greeks!C6&gt;0,Greeks!D6&gt;0),"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C8" s="1" t="str">
+        <f aca="false">IF(AND('European Pricer'!C7&gt;=MAX(0,Assumptions!E5*EXP(-Assumptions!E9*Assumptions!E7)-Assumptions!E6*EXP(-Assumptions!E8*Assumptions!E7)),'European Pricer'!C7&lt;=Assumptions!E5*EXP(-Assumptions!E9*Assumptions!E7)),"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C9" s="1" t="str">
+        <f aca="false">IF(COUNT(Portfolio!H5:M8)=24,"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C10" s="1" t="str">
+        <f aca="false">IF(COUNTIF(C5:C9,"FAIL")=0,"PASS","FAIL")</f>
+        <v>PASS</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:C2"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C5:C10">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>C5="PASS"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>C5="FAIL"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+      <formula>C5="REVIEW"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>C5="BREACH"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="B2:E9"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -1256,94 +2221,94 @@
   <sheetData>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>120</v>
+        <v>220</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="10" t="s">
-        <v>121</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>124</v>
+      <c r="B4" s="16" t="s">
+        <v>221</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>222</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="37" t="s">
-        <v>125</v>
-      </c>
-      <c r="C5" s="37" t="s">
-        <v>126</v>
-      </c>
-      <c r="D5" s="37" t="s">
+      <c r="B5" s="43" t="s">
+        <v>224</v>
+      </c>
+      <c r="C5" s="43" t="s">
+        <v>225</v>
+      </c>
+      <c r="D5" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="37" t="s">
-        <v>127</v>
+      <c r="E5" s="43" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="37" t="s">
-        <v>128</v>
-      </c>
-      <c r="C6" s="37" t="s">
-        <v>129</v>
-      </c>
-      <c r="D6" s="37" t="s">
-        <v>130</v>
-      </c>
-      <c r="E6" s="37" t="s">
-        <v>131</v>
+      <c r="B6" s="43" t="s">
+        <v>227</v>
+      </c>
+      <c r="C6" s="43" t="s">
+        <v>228</v>
+      </c>
+      <c r="D6" s="43" t="s">
+        <v>229</v>
+      </c>
+      <c r="E6" s="43" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="37" t="s">
-        <v>132</v>
-      </c>
-      <c r="C7" s="37" t="s">
-        <v>133</v>
-      </c>
-      <c r="D7" s="37" t="s">
+      <c r="B7" s="43" t="s">
+        <v>231</v>
+      </c>
+      <c r="C7" s="43" t="s">
+        <v>232</v>
+      </c>
+      <c r="D7" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="37" t="s">
-        <v>134</v>
+      <c r="E7" s="43" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="37" t="s">
-        <v>135</v>
-      </c>
-      <c r="C8" s="37" t="s">
-        <v>136</v>
-      </c>
-      <c r="D8" s="37" t="s">
+      <c r="B8" s="43" t="s">
+        <v>234</v>
+      </c>
+      <c r="C8" s="43" t="s">
+        <v>235</v>
+      </c>
+      <c r="D8" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="37" t="s">
-        <v>137</v>
+      <c r="E8" s="43" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="38" t="s">
-        <v>138</v>
-      </c>
-      <c r="C9" s="38" t="s">
-        <v>139</v>
-      </c>
-      <c r="D9" s="38" t="s">
+      <c r="B9" s="44" t="s">
+        <v>237</v>
+      </c>
+      <c r="C9" s="44" t="s">
+        <v>238</v>
+      </c>
+      <c r="D9" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="E9" s="38" t="s">
-        <v>140</v>
+      <c r="E9" s="44" t="s">
+        <v>239</v>
       </c>
     </row>
   </sheetData>
@@ -1360,7 +2325,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -1379,7 +2344,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>141</v>
+        <v>240</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -1388,236 +2353,236 @@
       <c r="G2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="10" t="s">
-        <v>142</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>145</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>147</v>
+      <c r="B4" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>241</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="39" t="s">
+      <c r="B5" s="45" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="39" t="s">
-        <v>148</v>
-      </c>
-      <c r="D5" s="39" t="s">
-        <v>139</v>
-      </c>
-      <c r="E5" s="39" t="s">
-        <v>149</v>
-      </c>
-      <c r="F5" s="39" t="s">
-        <v>150</v>
-      </c>
-      <c r="G5" s="39" t="s">
-        <v>151</v>
+      <c r="C5" s="45" t="s">
+        <v>246</v>
+      </c>
+      <c r="D5" s="45" t="s">
+        <v>238</v>
+      </c>
+      <c r="E5" s="45" t="s">
+        <v>247</v>
+      </c>
+      <c r="F5" s="45" t="s">
+        <v>248</v>
+      </c>
+      <c r="G5" s="45" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="39"/>
-      <c r="C6" s="39"/>
-      <c r="D6" s="39"/>
-      <c r="E6" s="39"/>
-      <c r="F6" s="39"/>
-      <c r="G6" s="39"/>
+      <c r="B6" s="45"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="45"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="39"/>
-      <c r="C7" s="39"/>
-      <c r="D7" s="39"/>
-      <c r="E7" s="39"/>
-      <c r="F7" s="39"/>
-      <c r="G7" s="39"/>
+      <c r="B7" s="45"/>
+      <c r="C7" s="45"/>
+      <c r="D7" s="45"/>
+      <c r="E7" s="45"/>
+      <c r="F7" s="45"/>
+      <c r="G7" s="45"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="39"/>
-      <c r="C8" s="39"/>
-      <c r="D8" s="39"/>
-      <c r="E8" s="39"/>
-      <c r="F8" s="39"/>
-      <c r="G8" s="39"/>
+      <c r="B8" s="45"/>
+      <c r="C8" s="45"/>
+      <c r="D8" s="45"/>
+      <c r="E8" s="45"/>
+      <c r="F8" s="45"/>
+      <c r="G8" s="45"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="39"/>
-      <c r="C9" s="39"/>
-      <c r="D9" s="39"/>
-      <c r="E9" s="39"/>
-      <c r="F9" s="39"/>
-      <c r="G9" s="39"/>
+      <c r="B9" s="45"/>
+      <c r="C9" s="45"/>
+      <c r="D9" s="45"/>
+      <c r="E9" s="45"/>
+      <c r="F9" s="45"/>
+      <c r="G9" s="45"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="39"/>
-      <c r="C10" s="39"/>
-      <c r="D10" s="39"/>
-      <c r="E10" s="39"/>
-      <c r="F10" s="39"/>
-      <c r="G10" s="39"/>
+      <c r="B10" s="45"/>
+      <c r="C10" s="45"/>
+      <c r="D10" s="45"/>
+      <c r="E10" s="45"/>
+      <c r="F10" s="45"/>
+      <c r="G10" s="45"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="39"/>
-      <c r="C11" s="39"/>
-      <c r="D11" s="39"/>
-      <c r="E11" s="39"/>
-      <c r="F11" s="39"/>
-      <c r="G11" s="39"/>
+      <c r="B11" s="45"/>
+      <c r="C11" s="45"/>
+      <c r="D11" s="45"/>
+      <c r="E11" s="45"/>
+      <c r="F11" s="45"/>
+      <c r="G11" s="45"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="39"/>
-      <c r="C12" s="39"/>
-      <c r="D12" s="39"/>
-      <c r="E12" s="39"/>
-      <c r="F12" s="39"/>
-      <c r="G12" s="39"/>
+      <c r="B12" s="45"/>
+      <c r="C12" s="45"/>
+      <c r="D12" s="45"/>
+      <c r="E12" s="45"/>
+      <c r="F12" s="45"/>
+      <c r="G12" s="45"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="39"/>
-      <c r="C13" s="39"/>
-      <c r="D13" s="39"/>
-      <c r="E13" s="39"/>
-      <c r="F13" s="39"/>
-      <c r="G13" s="39"/>
+      <c r="B13" s="45"/>
+      <c r="C13" s="45"/>
+      <c r="D13" s="45"/>
+      <c r="E13" s="45"/>
+      <c r="F13" s="45"/>
+      <c r="G13" s="45"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="39"/>
-      <c r="C14" s="39"/>
-      <c r="D14" s="39"/>
-      <c r="E14" s="39"/>
-      <c r="F14" s="39"/>
-      <c r="G14" s="39"/>
+      <c r="B14" s="45"/>
+      <c r="C14" s="45"/>
+      <c r="D14" s="45"/>
+      <c r="E14" s="45"/>
+      <c r="F14" s="45"/>
+      <c r="G14" s="45"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="39"/>
-      <c r="C15" s="39"/>
-      <c r="D15" s="39"/>
-      <c r="E15" s="39"/>
-      <c r="F15" s="39"/>
-      <c r="G15" s="39"/>
+      <c r="B15" s="45"/>
+      <c r="C15" s="45"/>
+      <c r="D15" s="45"/>
+      <c r="E15" s="45"/>
+      <c r="F15" s="45"/>
+      <c r="G15" s="45"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="39"/>
-      <c r="C16" s="39"/>
-      <c r="D16" s="39"/>
-      <c r="E16" s="39"/>
-      <c r="F16" s="39"/>
-      <c r="G16" s="39"/>
+      <c r="B16" s="45"/>
+      <c r="C16" s="45"/>
+      <c r="D16" s="45"/>
+      <c r="E16" s="45"/>
+      <c r="F16" s="45"/>
+      <c r="G16" s="45"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="39"/>
-      <c r="C17" s="39"/>
-      <c r="D17" s="39"/>
-      <c r="E17" s="39"/>
-      <c r="F17" s="39"/>
-      <c r="G17" s="39"/>
+      <c r="B17" s="45"/>
+      <c r="C17" s="45"/>
+      <c r="D17" s="45"/>
+      <c r="E17" s="45"/>
+      <c r="F17" s="45"/>
+      <c r="G17" s="45"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="39"/>
-      <c r="C18" s="39"/>
-      <c r="D18" s="39"/>
-      <c r="E18" s="39"/>
-      <c r="F18" s="39"/>
-      <c r="G18" s="39"/>
+      <c r="B18" s="45"/>
+      <c r="C18" s="45"/>
+      <c r="D18" s="45"/>
+      <c r="E18" s="45"/>
+      <c r="F18" s="45"/>
+      <c r="G18" s="45"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="39"/>
-      <c r="C19" s="39"/>
-      <c r="D19" s="39"/>
-      <c r="E19" s="39"/>
-      <c r="F19" s="39"/>
-      <c r="G19" s="39"/>
+      <c r="B19" s="45"/>
+      <c r="C19" s="45"/>
+      <c r="D19" s="45"/>
+      <c r="E19" s="45"/>
+      <c r="F19" s="45"/>
+      <c r="G19" s="45"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="39"/>
-      <c r="C20" s="39"/>
-      <c r="D20" s="39"/>
-      <c r="E20" s="39"/>
-      <c r="F20" s="39"/>
-      <c r="G20" s="39"/>
+      <c r="B20" s="45"/>
+      <c r="C20" s="45"/>
+      <c r="D20" s="45"/>
+      <c r="E20" s="45"/>
+      <c r="F20" s="45"/>
+      <c r="G20" s="45"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="39"/>
-      <c r="C21" s="39"/>
-      <c r="D21" s="39"/>
-      <c r="E21" s="39"/>
-      <c r="F21" s="39"/>
-      <c r="G21" s="39"/>
+      <c r="B21" s="45"/>
+      <c r="C21" s="45"/>
+      <c r="D21" s="45"/>
+      <c r="E21" s="45"/>
+      <c r="F21" s="45"/>
+      <c r="G21" s="45"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="39"/>
-      <c r="C22" s="39"/>
-      <c r="D22" s="39"/>
-      <c r="E22" s="39"/>
-      <c r="F22" s="39"/>
-      <c r="G22" s="39"/>
+      <c r="B22" s="45"/>
+      <c r="C22" s="45"/>
+      <c r="D22" s="45"/>
+      <c r="E22" s="45"/>
+      <c r="F22" s="45"/>
+      <c r="G22" s="45"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="39"/>
-      <c r="C23" s="39"/>
-      <c r="D23" s="39"/>
-      <c r="E23" s="39"/>
-      <c r="F23" s="39"/>
-      <c r="G23" s="39"/>
+      <c r="B23" s="45"/>
+      <c r="C23" s="45"/>
+      <c r="D23" s="45"/>
+      <c r="E23" s="45"/>
+      <c r="F23" s="45"/>
+      <c r="G23" s="45"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="39"/>
-      <c r="C24" s="39"/>
-      <c r="D24" s="39"/>
-      <c r="E24" s="39"/>
-      <c r="F24" s="39"/>
-      <c r="G24" s="39"/>
+      <c r="B24" s="45"/>
+      <c r="C24" s="45"/>
+      <c r="D24" s="45"/>
+      <c r="E24" s="45"/>
+      <c r="F24" s="45"/>
+      <c r="G24" s="45"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="39"/>
-      <c r="C25" s="39"/>
-      <c r="D25" s="39"/>
-      <c r="E25" s="39"/>
-      <c r="F25" s="39"/>
-      <c r="G25" s="39"/>
+      <c r="B25" s="45"/>
+      <c r="C25" s="45"/>
+      <c r="D25" s="45"/>
+      <c r="E25" s="45"/>
+      <c r="F25" s="45"/>
+      <c r="G25" s="45"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="39"/>
-      <c r="C26" s="39"/>
-      <c r="D26" s="39"/>
-      <c r="E26" s="39"/>
-      <c r="F26" s="39"/>
-      <c r="G26" s="39"/>
+      <c r="B26" s="45"/>
+      <c r="C26" s="45"/>
+      <c r="D26" s="45"/>
+      <c r="E26" s="45"/>
+      <c r="F26" s="45"/>
+      <c r="G26" s="45"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="39"/>
-      <c r="C27" s="39"/>
-      <c r="D27" s="39"/>
-      <c r="E27" s="39"/>
-      <c r="F27" s="39"/>
-      <c r="G27" s="39"/>
+      <c r="B27" s="45"/>
+      <c r="C27" s="45"/>
+      <c r="D27" s="45"/>
+      <c r="E27" s="45"/>
+      <c r="F27" s="45"/>
+      <c r="G27" s="45"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="39"/>
-      <c r="C28" s="39"/>
-      <c r="D28" s="39"/>
-      <c r="E28" s="39"/>
-      <c r="F28" s="39"/>
-      <c r="G28" s="39"/>
+      <c r="B28" s="45"/>
+      <c r="C28" s="45"/>
+      <c r="D28" s="45"/>
+      <c r="E28" s="45"/>
+      <c r="F28" s="45"/>
+      <c r="G28" s="45"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="39"/>
-      <c r="C29" s="39"/>
-      <c r="D29" s="39"/>
-      <c r="E29" s="39"/>
-      <c r="F29" s="39"/>
-      <c r="G29" s="39"/>
+      <c r="B29" s="45"/>
+      <c r="C29" s="45"/>
+      <c r="D29" s="45"/>
+      <c r="E29" s="45"/>
+      <c r="F29" s="45"/>
+      <c r="G29" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1638,6 +2603,1085 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="B2:F64"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="20"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B4" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="F13" s="14" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="E21" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="F21" s="14" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="C28" s="13"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="13"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B29" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C29" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D29" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="E29" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="F29" s="14" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B30" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B31" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B32" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B33" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B34" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B36" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="C36" s="13"/>
+      <c r="D36" s="13"/>
+      <c r="E36" s="13"/>
+      <c r="F36" s="13"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B37" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C37" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D37" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="E37" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="F37" s="14" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B38" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B39" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B40" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D40" s="1"/>
+      <c r="E40" s="1"/>
+      <c r="F40" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B41" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+      <c r="F41" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B42" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D42" s="1"/>
+      <c r="E42" s="1"/>
+      <c r="F42" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B44" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C44" s="13"/>
+      <c r="D44" s="13"/>
+      <c r="E44" s="13"/>
+      <c r="F44" s="13"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B45" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C45" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D45" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="E45" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="F45" s="14" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B46" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D46" s="1"/>
+      <c r="E46" s="1"/>
+      <c r="F46" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B47" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D47" s="1"/>
+      <c r="E47" s="1"/>
+      <c r="F47" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B48" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D48" s="1"/>
+      <c r="E48" s="1"/>
+      <c r="F48" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B49" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D49" s="1"/>
+      <c r="E49" s="1"/>
+      <c r="F49" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B50" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D50" s="1"/>
+      <c r="E50" s="1"/>
+      <c r="F50" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B52" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="C52" s="13"/>
+      <c r="D52" s="13"/>
+      <c r="E52" s="13"/>
+      <c r="F52" s="13"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B53" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C53" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D53" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="E53" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="F53" s="14" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B54" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D54" s="1"/>
+      <c r="E54" s="1"/>
+      <c r="F54" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B55" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D55" s="1"/>
+      <c r="E55" s="1"/>
+      <c r="F55" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B56" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D56" s="1"/>
+      <c r="E56" s="1"/>
+      <c r="F56" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B57" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D57" s="1"/>
+      <c r="E57" s="1"/>
+      <c r="F57" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B58" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D58" s="1"/>
+      <c r="E58" s="1"/>
+      <c r="F58" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B60" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="C60" s="13"/>
+      <c r="D60" s="13"/>
+      <c r="E60" s="13"/>
+      <c r="F60" s="13"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B61" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="C61" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="D61" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="E61" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="F61" s="14" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B62" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F62" s="1"/>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B63" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F63" s="1"/>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B64" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F64" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="C7:F7"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="C9:F9"/>
+    <mergeCell ref="C10:F10"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B44:F44"/>
+    <mergeCell ref="B52:F52"/>
+    <mergeCell ref="B60:F60"/>
+  </mergeCells>
+  <dataValidations count="6">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F14:F18" type="list">
+      <formula1>"OPEN,IN REVIEW,CLOSED,NOT APPLICABLE"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F22:F26" type="list">
+      <formula1>"OPEN,IN REVIEW,CLOSED,NOT APPLICABLE"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F30:F34" type="list">
+      <formula1>"OPEN,IN REVIEW,CLOSED,NOT APPLICABLE"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F38:F42" type="list">
+      <formula1>"OPEN,IN REVIEW,CLOSED,NOT APPLICABLE"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F46:F50" type="list">
+      <formula1>"OPEN,IN REVIEW,CLOSED,NOT APPLICABLE"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="F54:F58" type="list">
+      <formula1>"OPEN,IN REVIEW,CLOSED,NOT APPLICABLE"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="B2:I9"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="14"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="F4" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="G4" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="H4" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="I4" s="14" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="I5" s="1"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="I6" s="1"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="I7" s="1"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="I8" s="1"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="I9" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:I2"/>
+  </mergeCells>
+  <dataValidations count="2">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="H5:H54" type="list">
+      <formula1>"OPEN,IN REVIEW,REMEDIATED,ACCEPTED RISK,CLOSED"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G5:G54" type="list">
+      <formula1>"LOW,MEDIUM,HIGH,CRITICAL"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="B2:J8"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="15"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="F4" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="G4" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="H4" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="I4" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="J4" s="14" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="15" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="15" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="15" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="15" t="s">
+        <v>116</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:J2"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="J5:J40" type="list">
+      <formula1>"TO MAP,ACTIVE,STALE,EXCEPTION,RETIRED"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="B2:F15"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -1649,7 +3693,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>24</v>
+        <v>126</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -1657,218 +3701,218 @@
       <c r="F2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" s="10" t="s">
+      <c r="B4" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="D4" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>28</v>
+      <c r="E4" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5" s="11" t="n">
+        <v>131</v>
+      </c>
+      <c r="C5" s="17" t="n">
         <v>100</v>
       </c>
-      <c r="D5" s="12" t="n">
+      <c r="D5" s="18" t="n">
         <v>72</v>
       </c>
-      <c r="E5" s="13" t="n">
+      <c r="E5" s="19" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D5,C5)</f>
         <v>72</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>30</v>
+        <v>132</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C6" s="11" t="n">
+        <v>133</v>
+      </c>
+      <c r="C6" s="17" t="n">
         <v>100</v>
       </c>
-      <c r="D6" s="11" t="n">
+      <c r="D6" s="17" t="n">
         <v>100</v>
       </c>
-      <c r="E6" s="13" t="n">
+      <c r="E6" s="19" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D6,C6)</f>
         <v>100</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>30</v>
+        <v>132</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" s="14" t="n">
+        <v>134</v>
+      </c>
+      <c r="C7" s="20" t="n">
         <v>0.5</v>
       </c>
-      <c r="D7" s="14" t="n">
+      <c r="D7" s="20" t="n">
         <v>0.5</v>
       </c>
-      <c r="E7" s="15" t="n">
+      <c r="E7" s="21" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D7,C7)</f>
         <v>0.5</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>33</v>
+        <v>135</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" s="16" t="n">
+        <v>136</v>
+      </c>
+      <c r="C8" s="22" t="n">
         <v>0.04</v>
       </c>
-      <c r="D8" s="16" t="n">
+      <c r="D8" s="22" t="n">
         <v>0.03</v>
       </c>
-      <c r="E8" s="17" t="n">
+      <c r="E8" s="23" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D8,C8)</f>
         <v>0.03</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>35</v>
+        <v>137</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C9" s="16" t="n">
+        <v>138</v>
+      </c>
+      <c r="C9" s="22" t="n">
         <v>0.01</v>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="D9" s="22" t="n">
         <v>0.01</v>
       </c>
-      <c r="E9" s="17" t="n">
+      <c r="E9" s="23" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D9,C9)</f>
         <v>0.01</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>35</v>
+        <v>137</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10" s="16" t="n">
+        <v>139</v>
+      </c>
+      <c r="C10" s="22" t="n">
         <v>0.25</v>
       </c>
-      <c r="D10" s="18" t="n">
+      <c r="D10" s="24" t="n">
         <v>0.6</v>
       </c>
-      <c r="E10" s="17" t="n">
+      <c r="E10" s="23" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D10,C10)</f>
         <v>0.6</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>35</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11" s="11" t="n">
+        <v>140</v>
+      </c>
+      <c r="C11" s="17" t="n">
         <v>8.25</v>
       </c>
-      <c r="D11" s="12" t="n">
+      <c r="D11" s="18" t="n">
         <v>30</v>
       </c>
-      <c r="E11" s="13" t="n">
+      <c r="E11" s="19" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D11,C11)</f>
         <v>30</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>30</v>
+        <v>132</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C12" s="19" t="n">
+        <v>141</v>
+      </c>
+      <c r="C12" s="25" t="n">
         <v>100</v>
       </c>
-      <c r="D12" s="19" t="n">
+      <c r="D12" s="25" t="n">
         <v>100</v>
       </c>
-      <c r="E12" s="20" t="n">
+      <c r="E12" s="26" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D12,C12)</f>
         <v>100</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>40</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C13" s="19" t="n">
+        <v>143</v>
+      </c>
+      <c r="C13" s="25" t="n">
         <v>10</v>
       </c>
-      <c r="D13" s="19" t="n">
+      <c r="D13" s="25" t="n">
         <v>10</v>
       </c>
-      <c r="E13" s="20" t="n">
+      <c r="E13" s="26" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D13,C13)</f>
         <v>10</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>42</v>
+        <v>144</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C14" s="21" t="n">
+        <v>145</v>
+      </c>
+      <c r="C14" s="27" t="n">
         <v>-0.2</v>
       </c>
-      <c r="D14" s="22" t="n">
+      <c r="D14" s="28" t="n">
         <v>-0.5</v>
       </c>
-      <c r="E14" s="23" t="n">
+      <c r="E14" s="29" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D14,C14)</f>
         <v>-0.5</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>44</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C15" s="21" t="n">
+        <v>147</v>
+      </c>
+      <c r="C15" s="27" t="n">
         <v>0.02</v>
       </c>
-      <c r="D15" s="21" t="n">
+      <c r="D15" s="27" t="n">
         <v>0.04</v>
       </c>
-      <c r="E15" s="23" t="n">
+      <c r="E15" s="29" t="n">
         <f aca="false">IF(Cover!$C$9="Downside",D15,C15)</f>
         <v>0.04</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>46</v>
+        <v>148</v>
       </c>
     </row>
   </sheetData>
@@ -1885,7 +3929,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -1903,7 +3947,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>47</v>
+        <v>149</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -1911,155 +3955,155 @@
       <c r="F2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>52</v>
+      <c r="B4" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>152</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C5" s="24" t="n">
+        <v>154</v>
+      </c>
+      <c r="C5" s="30" t="n">
         <f aca="false">(LN(Assumptions!E5/Assumptions!E6)+(Assumptions!E8-Assumptions!E9+0.5*Assumptions!E10^2)*Assumptions!E7)/(Assumptions!E10*SQRT(Assumptions!E7))</f>
         <v>-0.538589250948773</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>54</v>
+        <v>155</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>55</v>
+        <v>156</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C6" s="24" t="n">
+        <v>157</v>
+      </c>
+      <c r="C6" s="30" t="n">
         <f aca="false">C5-Assumptions!E10*SQRT(Assumptions!E7)</f>
         <v>-0.962853319660701</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>54</v>
+        <v>155</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>57</v>
+        <v>158</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C7" s="13" t="n">
+        <v>159</v>
+      </c>
+      <c r="C7" s="19" t="n">
         <f aca="false">Assumptions!E5*EXP(-Assumptions!E9*Assumptions!E7)*NORMSDIST(C5)-Assumptions!E6*EXP(-Assumptions!E8*Assumptions!E7)*NORMSDIST(C6)</f>
         <v>4.60894596936213</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>30</v>
+        <v>132</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>59</v>
+        <v>160</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C8" s="13" t="n">
+        <v>161</v>
+      </c>
+      <c r="C8" s="19" t="n">
         <f aca="false">Assumptions!E6*EXP(-Assumptions!E8*Assumptions!E7)*NORMSDIST(-C6)-Assumptions!E5*EXP(-Assumptions!E9*Assumptions!E7)*NORMSDIST(-C5)</f>
         <v>31.4792414277953</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>30</v>
+        <v>132</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>59</v>
+        <v>160</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C9" s="13" t="n">
+        <v>162</v>
+      </c>
+      <c r="C9" s="19" t="n">
         <f aca="false">MAX(0,Assumptions!E5-Assumptions!E6)</f>
         <v>0</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>30</v>
+        <v>132</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>62</v>
+        <v>163</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="C10" s="13" t="n">
+        <v>164</v>
+      </c>
+      <c r="C10" s="19" t="n">
         <f aca="false">MAX(0,Assumptions!E6-Assumptions!E5)</f>
         <v>28</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>30</v>
+        <v>132</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>62</v>
+        <v>163</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C11" s="13" t="n">
+        <v>165</v>
+      </c>
+      <c r="C11" s="19" t="n">
         <f aca="false">C7-C9</f>
         <v>4.60894596936213</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>30</v>
+        <v>132</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>65</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C12" s="13" t="n">
+        <v>167</v>
+      </c>
+      <c r="C12" s="19" t="n">
         <f aca="false">C8-C10</f>
         <v>3.47924142779526</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>30</v>
+        <v>132</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>65</v>
+        <v>166</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C13" s="24" t="n">
+        <v>168</v>
+      </c>
+      <c r="C13" s="30" t="n">
         <f aca="false">C7-C8-(Assumptions!E5*EXP(-Assumptions!E9*Assumptions!E7)-Assumptions!E6*EXP(-Assumptions!E8*Assumptions!E7))</f>
         <v>0</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>30</v>
+        <v>132</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>68</v>
+        <v>169</v>
       </c>
       <c r="F13" s="1" t="str">
         <f aca="false">IF(ABS(C13)&lt;0.000001,"PASS","FAIL")</f>
@@ -2094,7 +4138,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -2108,7 +4152,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>69</v>
+        <v>170</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -2117,45 +4161,45 @@
       <c r="G2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>75</v>
+      <c r="B4" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>172</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>175</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="C5" s="16" t="n">
+      <c r="C5" s="22" t="n">
         <v>0.2</v>
       </c>
-      <c r="D5" s="25" t="n">
+      <c r="D5" s="31" t="n">
         <f aca="false">Assumptions!$E$5*EXP(-Assumptions!$E$9*Assumptions!$E$7)*NORMSDIST((LN(Assumptions!$E$5/Assumptions!$E$6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*C5^2)*Assumptions!$E$7)/(C5*SQRT(Assumptions!$E$7)))-Assumptions!$E$6*EXP(-Assumptions!$E$8*Assumptions!$E$7)*NORMSDIST(((LN(Assumptions!$E$5/Assumptions!$E$6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*C5^2)*Assumptions!$E$7)/(C5*SQRT(Assumptions!$E$7)))-C5*SQRT(Assumptions!$E$7))</f>
         <v>0.0498947790933063</v>
       </c>
-      <c r="E5" s="13" t="n">
+      <c r="E5" s="19" t="n">
         <f aca="false">Assumptions!$E$11</f>
         <v>30</v>
       </c>
-      <c r="F5" s="25" t="n">
+      <c r="F5" s="31" t="n">
         <f aca="false">D5-E5</f>
         <v>-29.9501052209067</v>
       </c>
-      <c r="G5" s="26" t="n">
+      <c r="G5" s="32" t="n">
         <f aca="false">Assumptions!$E$5*EXP(-Assumptions!$E$9*Assumptions!$E$7)*(EXP(-(((LN(Assumptions!$E$5/Assumptions!$E$6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*C5^2)*Assumptions!$E$7)/(C5*SQRT(Assumptions!$E$7)))^2)/2)/SQRT(2*PI()))*SQRT(Assumptions!$E$7)</f>
         <v>1.8715837771619</v>
       </c>
@@ -2164,23 +4208,23 @@
       <c r="B6" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="27" t="n">
+      <c r="C6" s="33" t="n">
         <f aca="false">MAX(0.0001,C5-F5/MAX(0.000001,G5))</f>
         <v>16.2025458578849</v>
       </c>
-      <c r="D6" s="25" t="n">
+      <c r="D6" s="31" t="n">
         <f aca="false">Assumptions!$E$5*EXP(-Assumptions!$E$9*Assumptions!$E$7)*NORMSDIST((LN(Assumptions!$E$5/Assumptions!$E$6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*C6^2)*Assumptions!$E$7)/(C6*SQRT(Assumptions!$E$7)))-Assumptions!$E$6*EXP(-Assumptions!$E$8*Assumptions!$E$7)*NORMSDIST(((LN(Assumptions!$E$5/Assumptions!$E$6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*C6^2)*Assumptions!$E$7)/(C6*SQRT(Assumptions!$E$7)))-C6*SQRT(Assumptions!$E$7))</f>
         <v>71.6408976508133</v>
       </c>
-      <c r="E6" s="13" t="n">
+      <c r="E6" s="19" t="n">
         <f aca="false">Assumptions!$E$11</f>
         <v>30</v>
       </c>
-      <c r="F6" s="25" t="n">
+      <c r="F6" s="31" t="n">
         <f aca="false">D6-E6</f>
         <v>41.6408976508133</v>
       </c>
-      <c r="G6" s="26" t="n">
+      <c r="G6" s="32" t="n">
         <f aca="false">Assumptions!$E$5*EXP(-Assumptions!$E$9*Assumptions!$E$7)*(EXP(-(((LN(Assumptions!$E$5/Assumptions!$E$6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*C6^2)*Assumptions!$E$7)/(C6*SQRT(Assumptions!$E$7)))^2)/2)/SQRT(2*PI()))*SQRT(Assumptions!$E$7)</f>
         <v>1.77335706347096E-006</v>
       </c>
@@ -2189,23 +4233,23 @@
       <c r="B7" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C7" s="27" t="n">
+      <c r="C7" s="33" t="n">
         <f aca="false">MAX(0.0001,C6-F6/MAX(0.000001,G6))</f>
         <v>0.0001</v>
       </c>
-      <c r="D7" s="25" t="n">
+      <c r="D7" s="31" t="n">
         <f aca="false">Assumptions!$E$5*EXP(-Assumptions!$E$9*Assumptions!$E$7)*NORMSDIST((LN(Assumptions!$E$5/Assumptions!$E$6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*C7^2)*Assumptions!$E$7)/(C7*SQRT(Assumptions!$E$7)))-Assumptions!$E$6*EXP(-Assumptions!$E$8*Assumptions!$E$7)*NORMSDIST(((LN(Assumptions!$E$5/Assumptions!$E$6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*C7^2)*Assumptions!$E$7)/(C7*SQRT(Assumptions!$E$7)))-C7*SQRT(Assumptions!$E$7))</f>
         <v>0</v>
       </c>
-      <c r="E7" s="13" t="n">
+      <c r="E7" s="19" t="n">
         <f aca="false">Assumptions!$E$11</f>
         <v>30</v>
       </c>
-      <c r="F7" s="25" t="n">
+      <c r="F7" s="31" t="n">
         <f aca="false">D7-E7</f>
         <v>-30</v>
       </c>
-      <c r="G7" s="26" t="n">
+      <c r="G7" s="32" t="n">
         <f aca="false">Assumptions!$E$5*EXP(-Assumptions!$E$9*Assumptions!$E$7)*(EXP(-(((LN(Assumptions!$E$5/Assumptions!$E$6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*C7^2)*Assumptions!$E$7)/(C7*SQRT(Assumptions!$E$7)))^2)/2)/SQRT(2*PI()))*SQRT(Assumptions!$E$7)</f>
         <v>0</v>
       </c>
@@ -2214,23 +4258,23 @@
       <c r="B8" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="C8" s="27" t="n">
+      <c r="C8" s="33" t="n">
         <f aca="false">MAX(0.0001,C7-F7/MAX(0.000001,G7))</f>
         <v>30000000.0001</v>
       </c>
-      <c r="D8" s="25" t="n">
+      <c r="D8" s="31" t="n">
         <f aca="false">Assumptions!$E$5*EXP(-Assumptions!$E$9*Assumptions!$E$7)*NORMSDIST((LN(Assumptions!$E$5/Assumptions!$E$6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*C8^2)*Assumptions!$E$7)/(C8*SQRT(Assumptions!$E$7)))-Assumptions!$E$6*EXP(-Assumptions!$E$8*Assumptions!$E$7)*NORMSDIST(((LN(Assumptions!$E$5/Assumptions!$E$6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*C8^2)*Assumptions!$E$7)/(C8*SQRT(Assumptions!$E$7)))-C8*SQRT(Assumptions!$E$7))</f>
         <v>71.6408985018731</v>
       </c>
-      <c r="E8" s="13" t="n">
+      <c r="E8" s="19" t="n">
         <f aca="false">Assumptions!$E$11</f>
         <v>30</v>
       </c>
-      <c r="F8" s="25" t="n">
+      <c r="F8" s="31" t="n">
         <f aca="false">D8-E8</f>
         <v>41.6408985018731</v>
       </c>
-      <c r="G8" s="26" t="n">
+      <c r="G8" s="32" t="n">
         <f aca="false">Assumptions!$E$5*EXP(-Assumptions!$E$9*Assumptions!$E$7)*(EXP(-(((LN(Assumptions!$E$5/Assumptions!$E$6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*C8^2)*Assumptions!$E$7)/(C8*SQRT(Assumptions!$E$7)))^2)/2)/SQRT(2*PI()))*SQRT(Assumptions!$E$7)</f>
         <v>0</v>
       </c>
@@ -2239,23 +4283,23 @@
       <c r="B9" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="C9" s="27" t="n">
+      <c r="C9" s="33" t="n">
         <f aca="false">MAX(0.0001,C8-F8/MAX(0.000001,G8))</f>
         <v>0.0001</v>
       </c>
-      <c r="D9" s="25" t="n">
+      <c r="D9" s="31" t="n">
         <f aca="false">Assumptions!$E$5*EXP(-Assumptions!$E$9*Assumptions!$E$7)*NORMSDIST((LN(Assumptions!$E$5/Assumptions!$E$6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*C9^2)*Assumptions!$E$7)/(C9*SQRT(Assumptions!$E$7)))-Assumptions!$E$6*EXP(-Assumptions!$E$8*Assumptions!$E$7)*NORMSDIST(((LN(Assumptions!$E$5/Assumptions!$E$6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*C9^2)*Assumptions!$E$7)/(C9*SQRT(Assumptions!$E$7)))-C9*SQRT(Assumptions!$E$7))</f>
         <v>0</v>
       </c>
-      <c r="E9" s="13" t="n">
+      <c r="E9" s="19" t="n">
         <f aca="false">Assumptions!$E$11</f>
         <v>30</v>
       </c>
-      <c r="F9" s="25" t="n">
+      <c r="F9" s="31" t="n">
         <f aca="false">D9-E9</f>
         <v>-30</v>
       </c>
-      <c r="G9" s="26" t="n">
+      <c r="G9" s="32" t="n">
         <f aca="false">Assumptions!$E$5*EXP(-Assumptions!$E$9*Assumptions!$E$7)*(EXP(-(((LN(Assumptions!$E$5/Assumptions!$E$6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*C9^2)*Assumptions!$E$7)/(C9*SQRT(Assumptions!$E$7)))^2)/2)/SQRT(2*PI()))*SQRT(Assumptions!$E$7)</f>
         <v>0</v>
       </c>
@@ -2264,23 +4308,23 @@
       <c r="B10" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C10" s="27" t="n">
+      <c r="C10" s="33" t="n">
         <f aca="false">MAX(0.0001,C9-F9/MAX(0.000001,G9))</f>
         <v>30000000.0001</v>
       </c>
-      <c r="D10" s="25" t="n">
+      <c r="D10" s="31" t="n">
         <f aca="false">Assumptions!$E$5*EXP(-Assumptions!$E$9*Assumptions!$E$7)*NORMSDIST((LN(Assumptions!$E$5/Assumptions!$E$6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*C10^2)*Assumptions!$E$7)/(C10*SQRT(Assumptions!$E$7)))-Assumptions!$E$6*EXP(-Assumptions!$E$8*Assumptions!$E$7)*NORMSDIST(((LN(Assumptions!$E$5/Assumptions!$E$6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*C10^2)*Assumptions!$E$7)/(C10*SQRT(Assumptions!$E$7)))-C10*SQRT(Assumptions!$E$7))</f>
         <v>71.6408985018731</v>
       </c>
-      <c r="E10" s="13" t="n">
+      <c r="E10" s="19" t="n">
         <f aca="false">Assumptions!$E$11</f>
         <v>30</v>
       </c>
-      <c r="F10" s="25" t="n">
+      <c r="F10" s="31" t="n">
         <f aca="false">D10-E10</f>
         <v>41.6408985018731</v>
       </c>
-      <c r="G10" s="26" t="n">
+      <c r="G10" s="32" t="n">
         <f aca="false">Assumptions!$E$5*EXP(-Assumptions!$E$9*Assumptions!$E$7)*(EXP(-(((LN(Assumptions!$E$5/Assumptions!$E$6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*C10^2)*Assumptions!$E$7)/(C10*SQRT(Assumptions!$E$7)))^2)/2)/SQRT(2*PI()))*SQRT(Assumptions!$E$7)</f>
         <v>0</v>
       </c>
@@ -2289,23 +4333,23 @@
       <c r="B11" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C11" s="27" t="n">
+      <c r="C11" s="33" t="n">
         <f aca="false">MAX(0.0001,C10-F10/MAX(0.000001,G10))</f>
         <v>0.0001</v>
       </c>
-      <c r="D11" s="25" t="n">
+      <c r="D11" s="31" t="n">
         <f aca="false">Assumptions!$E$5*EXP(-Assumptions!$E$9*Assumptions!$E$7)*NORMSDIST((LN(Assumptions!$E$5/Assumptions!$E$6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*C11^2)*Assumptions!$E$7)/(C11*SQRT(Assumptions!$E$7)))-Assumptions!$E$6*EXP(-Assumptions!$E$8*Assumptions!$E$7)*NORMSDIST(((LN(Assumptions!$E$5/Assumptions!$E$6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*C11^2)*Assumptions!$E$7)/(C11*SQRT(Assumptions!$E$7)))-C11*SQRT(Assumptions!$E$7))</f>
         <v>0</v>
       </c>
-      <c r="E11" s="13" t="n">
+      <c r="E11" s="19" t="n">
         <f aca="false">Assumptions!$E$11</f>
         <v>30</v>
       </c>
-      <c r="F11" s="25" t="n">
+      <c r="F11" s="31" t="n">
         <f aca="false">D11-E11</f>
         <v>-30</v>
       </c>
-      <c r="G11" s="26" t="n">
+      <c r="G11" s="32" t="n">
         <f aca="false">Assumptions!$E$5*EXP(-Assumptions!$E$9*Assumptions!$E$7)*(EXP(-(((LN(Assumptions!$E$5/Assumptions!$E$6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*C11^2)*Assumptions!$E$7)/(C11*SQRT(Assumptions!$E$7)))^2)/2)/SQRT(2*PI()))*SQRT(Assumptions!$E$7)</f>
         <v>0</v>
       </c>
@@ -2314,23 +4358,23 @@
       <c r="B12" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C12" s="27" t="n">
+      <c r="C12" s="33" t="n">
         <f aca="false">MAX(0.0001,C11-F11/MAX(0.000001,G11))</f>
         <v>30000000.0001</v>
       </c>
-      <c r="D12" s="25" t="n">
+      <c r="D12" s="31" t="n">
         <f aca="false">Assumptions!$E$5*EXP(-Assumptions!$E$9*Assumptions!$E$7)*NORMSDIST((LN(Assumptions!$E$5/Assumptions!$E$6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*C12^2)*Assumptions!$E$7)/(C12*SQRT(Assumptions!$E$7)))-Assumptions!$E$6*EXP(-Assumptions!$E$8*Assumptions!$E$7)*NORMSDIST(((LN(Assumptions!$E$5/Assumptions!$E$6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*C12^2)*Assumptions!$E$7)/(C12*SQRT(Assumptions!$E$7)))-C12*SQRT(Assumptions!$E$7))</f>
         <v>71.6408985018731</v>
       </c>
-      <c r="E12" s="13" t="n">
+      <c r="E12" s="19" t="n">
         <f aca="false">Assumptions!$E$11</f>
         <v>30</v>
       </c>
-      <c r="F12" s="25" t="n">
+      <c r="F12" s="31" t="n">
         <f aca="false">D12-E12</f>
         <v>41.6408985018731</v>
       </c>
-      <c r="G12" s="26" t="n">
+      <c r="G12" s="32" t="n">
         <f aca="false">Assumptions!$E$5*EXP(-Assumptions!$E$9*Assumptions!$E$7)*(EXP(-(((LN(Assumptions!$E$5/Assumptions!$E$6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*C12^2)*Assumptions!$E$7)/(C12*SQRT(Assumptions!$E$7)))^2)/2)/SQRT(2*PI()))*SQRT(Assumptions!$E$7)</f>
         <v>0</v>
       </c>
@@ -2339,23 +4383,23 @@
       <c r="B13" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C13" s="27" t="n">
+      <c r="C13" s="33" t="n">
         <f aca="false">MAX(0.0001,C12-F12/MAX(0.000001,G12))</f>
         <v>0.0001</v>
       </c>
-      <c r="D13" s="25" t="n">
+      <c r="D13" s="31" t="n">
         <f aca="false">Assumptions!$E$5*EXP(-Assumptions!$E$9*Assumptions!$E$7)*NORMSDIST((LN(Assumptions!$E$5/Assumptions!$E$6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*C13^2)*Assumptions!$E$7)/(C13*SQRT(Assumptions!$E$7)))-Assumptions!$E$6*EXP(-Assumptions!$E$8*Assumptions!$E$7)*NORMSDIST(((LN(Assumptions!$E$5/Assumptions!$E$6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*C13^2)*Assumptions!$E$7)/(C13*SQRT(Assumptions!$E$7)))-C13*SQRT(Assumptions!$E$7))</f>
         <v>0</v>
       </c>
-      <c r="E13" s="13" t="n">
+      <c r="E13" s="19" t="n">
         <f aca="false">Assumptions!$E$11</f>
         <v>30</v>
       </c>
-      <c r="F13" s="25" t="n">
+      <c r="F13" s="31" t="n">
         <f aca="false">D13-E13</f>
         <v>-30</v>
       </c>
-      <c r="G13" s="26" t="n">
+      <c r="G13" s="32" t="n">
         <f aca="false">Assumptions!$E$5*EXP(-Assumptions!$E$9*Assumptions!$E$7)*(EXP(-(((LN(Assumptions!$E$5/Assumptions!$E$6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*C13^2)*Assumptions!$E$7)/(C13*SQRT(Assumptions!$E$7)))^2)/2)/SQRT(2*PI()))*SQRT(Assumptions!$E$7)</f>
         <v>0</v>
       </c>
@@ -2364,39 +4408,39 @@
       <c r="B14" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C14" s="27" t="n">
+      <c r="C14" s="33" t="n">
         <f aca="false">MAX(0.0001,C13-F13/MAX(0.000001,G13))</f>
         <v>30000000.0001</v>
       </c>
-      <c r="D14" s="25" t="n">
+      <c r="D14" s="31" t="n">
         <f aca="false">Assumptions!$E$5*EXP(-Assumptions!$E$9*Assumptions!$E$7)*NORMSDIST((LN(Assumptions!$E$5/Assumptions!$E$6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*C14^2)*Assumptions!$E$7)/(C14*SQRT(Assumptions!$E$7)))-Assumptions!$E$6*EXP(-Assumptions!$E$8*Assumptions!$E$7)*NORMSDIST(((LN(Assumptions!$E$5/Assumptions!$E$6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*C14^2)*Assumptions!$E$7)/(C14*SQRT(Assumptions!$E$7)))-C14*SQRT(Assumptions!$E$7))</f>
         <v>71.6408985018731</v>
       </c>
-      <c r="E14" s="13" t="n">
+      <c r="E14" s="19" t="n">
         <f aca="false">Assumptions!$E$11</f>
         <v>30</v>
       </c>
-      <c r="F14" s="25" t="n">
+      <c r="F14" s="31" t="n">
         <f aca="false">D14-E14</f>
         <v>41.6408985018731</v>
       </c>
-      <c r="G14" s="26" t="n">
+      <c r="G14" s="32" t="n">
         <f aca="false">Assumptions!$E$5*EXP(-Assumptions!$E$9*Assumptions!$E$7)*(EXP(-(((LN(Assumptions!$E$5/Assumptions!$E$6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*C14^2)*Assumptions!$E$7)/(C14*SQRT(Assumptions!$E$7)))^2)/2)/SQRT(2*PI()))*SQRT(Assumptions!$E$7)</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C17" s="27" t="n">
+        <v>177</v>
+      </c>
+      <c r="C17" s="33" t="n">
         <f aca="false">C14</f>
         <v>30000000.0001</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="E17" s="25" t="n">
+        <v>178</v>
+      </c>
+      <c r="E17" s="31" t="n">
         <f aca="false">ABS(F14)</f>
         <v>41.6408985018731</v>
       </c>
@@ -2415,7 +4459,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -2431,104 +4475,104 @@
   <sheetData>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>78</v>
+        <v>179</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>82</v>
+      <c r="B4" s="16" t="s">
+        <v>180</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>181</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>182</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="C5" s="28" t="n">
+        <v>184</v>
+      </c>
+      <c r="C5" s="34" t="n">
         <f aca="false">EXP(-Assumptions!$E$9*Assumptions!$E$7)*NORMSDIST('European Pricer'!$C$5)</f>
         <v>0.2936134097194</v>
       </c>
-      <c r="D5" s="28" t="n">
+      <c r="D5" s="34" t="n">
         <f aca="false">EXP(-Assumptions!$E$9*Assumptions!$E$7)*(NORMSDIST('European Pricer'!$C$5)-1)</f>
         <v>-0.701399069473283</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>84</v>
+        <v>185</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="C6" s="28" t="n">
+        <v>186</v>
+      </c>
+      <c r="C6" s="34" t="n">
         <f aca="false">EXP(-Assumptions!$E$9*Assumptions!$E$7)*(EXP(-(('European Pricer'!$C$5)^2)/2)/SQRT(2*PI()))/(Assumptions!$E$5*Assumptions!$E$10*SQRT(Assumptions!$E$7))</f>
         <v>0.0112403575020123</v>
       </c>
-      <c r="D6" s="28" t="n">
+      <c r="D6" s="34" t="n">
         <f aca="false">C6</f>
         <v>0.0112403575020123</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>86</v>
+        <v>187</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C7" s="28" t="n">
+        <v>176</v>
+      </c>
+      <c r="C7" s="34" t="n">
         <f aca="false">Assumptions!$E$5*EXP(-Assumptions!$E$9*Assumptions!$E$7)*(EXP(-(('European Pricer'!$C$5)^2)/2)/SQRT(2*PI()))*SQRT(Assumptions!$E$7)</f>
         <v>17.4810039871296</v>
       </c>
-      <c r="D7" s="28" t="n">
+      <c r="D7" s="34" t="n">
         <f aca="false">C7</f>
         <v>17.4810039871296</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>87</v>
+        <v>188</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="C8" s="28" t="n">
+        <v>189</v>
+      </c>
+      <c r="C8" s="34" t="n">
         <f aca="false">-Assumptions!$E$5*EXP(-Assumptions!$E$9*Assumptions!$E$7)*(EXP(-(('European Pricer'!$C$5)^2)/2)/SQRT(2*PI()))*Assumptions!$E$10/(2*SQRT(Assumptions!$E$7))-Assumptions!$E$8*Assumptions!$E$6*EXP(-Assumptions!$E$8*Assumptions!$E$7)*NORMSDIST('European Pricer'!$C$6)+Assumptions!$E$9*Assumptions!$E$5*EXP(-Assumptions!$E$9*Assumptions!$E$7)*NORMSDIST('European Pricer'!$C$5)</f>
         <v>-10.7731373231928</v>
       </c>
-      <c r="D8" s="28" t="n">
+      <c r="D8" s="34" t="n">
         <f aca="false">-Assumptions!$E$5*EXP(-Assumptions!$E$9*Assumptions!$E$7)*(EXP(-(('European Pricer'!$C$5)^2)/2)/SQRT(2*PI()))*Assumptions!$E$10/(2*SQRT(Assumptions!$E$7))+Assumptions!$E$8*Assumptions!$E$6*EXP(-Assumptions!$E$8*Assumptions!$E$7)*NORMSDIST(-'European Pricer'!$C$6)-Assumptions!$E$9*Assumptions!$E$5*EXP(-Assumptions!$E$9*Assumptions!$E$7)*NORMSDIST(-'European Pricer'!$C$5)</f>
         <v>-8.53421048940236</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>89</v>
+        <v>190</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="C9" s="28" t="n">
+        <v>191</v>
+      </c>
+      <c r="C9" s="34" t="n">
         <f aca="false">Assumptions!$E$7*Assumptions!$E$6*EXP(-Assumptions!$E$8*Assumptions!$E$7)*NORMSDIST('European Pricer'!$C$6)</f>
         <v>8.26560976521733</v>
       </c>
-      <c r="D9" s="28" t="n">
+      <c r="D9" s="34" t="n">
         <f aca="false">-Assumptions!$E$7*Assumptions!$E$6*EXP(-Assumptions!$E$8*Assumptions!$E$7)*NORMSDIST(-'European Pricer'!$C$6)</f>
         <v>-40.9899872149358</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>91</v>
+        <v>192</v>
       </c>
     </row>
   </sheetData>
@@ -2545,7 +4589,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -2560,7 +4604,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>92</v>
+        <v>193</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -2569,121 +4613,121 @@
       <c r="G2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="C4" s="10" t="n">
+      <c r="B4" s="16" t="s">
+        <v>194</v>
+      </c>
+      <c r="C4" s="16" t="n">
         <v>80</v>
       </c>
-      <c r="D4" s="10" t="n">
+      <c r="D4" s="16" t="n">
         <v>90</v>
       </c>
-      <c r="E4" s="10" t="n">
+      <c r="E4" s="16" t="n">
         <v>100</v>
       </c>
-      <c r="F4" s="10" t="n">
+      <c r="F4" s="16" t="n">
         <v>110</v>
       </c>
-      <c r="G4" s="10" t="n">
+      <c r="G4" s="16" t="n">
         <v>120</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="29" t="n">
+      <c r="B5" s="35" t="n">
         <v>0.25</v>
       </c>
-      <c r="C5" s="27" t="n">
+      <c r="C5" s="33" t="n">
         <f aca="false">MAX(0.01,Assumptions!$E$10+Assumptions!$E$14*(C$4/Assumptions!$E$5-1)+Assumptions!$E$15*LN($B5/Assumptions!$E$7))</f>
         <v>0.516718557222047</v>
       </c>
-      <c r="D5" s="27" t="n">
+      <c r="D5" s="33" t="n">
         <f aca="false">MAX(0.01,Assumptions!$E$10+Assumptions!$E$14*(D$4/Assumptions!$E$5-1)+Assumptions!$E$15*LN($B5/Assumptions!$E$7))</f>
         <v>0.447274112777602</v>
       </c>
-      <c r="E5" s="27" t="n">
+      <c r="E5" s="33" t="n">
         <f aca="false">MAX(0.01,Assumptions!$E$10+Assumptions!$E$14*(E$4/Assumptions!$E$5-1)+Assumptions!$E$15*LN($B5/Assumptions!$E$7))</f>
         <v>0.377829668333158</v>
       </c>
-      <c r="F5" s="27" t="n">
+      <c r="F5" s="33" t="n">
         <f aca="false">MAX(0.01,Assumptions!$E$10+Assumptions!$E$14*(F$4/Assumptions!$E$5-1)+Assumptions!$E$15*LN($B5/Assumptions!$E$7))</f>
         <v>0.308385223888713</v>
       </c>
-      <c r="G5" s="27" t="n">
+      <c r="G5" s="33" t="n">
         <f aca="false">MAX(0.01,Assumptions!$E$10+Assumptions!$E$14*(G$4/Assumptions!$E$5-1)+Assumptions!$E$15*LN($B5/Assumptions!$E$7))</f>
         <v>0.238940779444269</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="29" t="n">
+      <c r="B6" s="35" t="n">
         <v>0.5</v>
       </c>
-      <c r="C6" s="27" t="n">
+      <c r="C6" s="33" t="n">
         <f aca="false">MAX(0.01,Assumptions!$E$10+Assumptions!$E$14*(C$4/Assumptions!$E$5-1)+Assumptions!$E$15*LN($B6/Assumptions!$E$7))</f>
         <v>0.544444444444444</v>
       </c>
-      <c r="D6" s="27" t="n">
+      <c r="D6" s="33" t="n">
         <f aca="false">MAX(0.01,Assumptions!$E$10+Assumptions!$E$14*(D$4/Assumptions!$E$5-1)+Assumptions!$E$15*LN($B6/Assumptions!$E$7))</f>
         <v>0.475</v>
       </c>
-      <c r="E6" s="27" t="n">
+      <c r="E6" s="33" t="n">
         <f aca="false">MAX(0.01,Assumptions!$E$10+Assumptions!$E$14*(E$4/Assumptions!$E$5-1)+Assumptions!$E$15*LN($B6/Assumptions!$E$7))</f>
         <v>0.405555555555556</v>
       </c>
-      <c r="F6" s="27" t="n">
+      <c r="F6" s="33" t="n">
         <f aca="false">MAX(0.01,Assumptions!$E$10+Assumptions!$E$14*(F$4/Assumptions!$E$5-1)+Assumptions!$E$15*LN($B6/Assumptions!$E$7))</f>
         <v>0.336111111111111</v>
       </c>
-      <c r="G6" s="27" t="n">
+      <c r="G6" s="33" t="n">
         <f aca="false">MAX(0.01,Assumptions!$E$10+Assumptions!$E$14*(G$4/Assumptions!$E$5-1)+Assumptions!$E$15*LN($B6/Assumptions!$E$7))</f>
         <v>0.266666666666667</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="29" t="n">
+      <c r="B7" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="27" t="n">
+      <c r="C7" s="33" t="n">
         <f aca="false">MAX(0.01,Assumptions!$E$10+Assumptions!$E$14*(C$4/Assumptions!$E$5-1)+Assumptions!$E$15*LN($B7/Assumptions!$E$7))</f>
         <v>0.572170331666842</v>
       </c>
-      <c r="D7" s="27" t="n">
+      <c r="D7" s="33" t="n">
         <f aca="false">MAX(0.01,Assumptions!$E$10+Assumptions!$E$14*(D$4/Assumptions!$E$5-1)+Assumptions!$E$15*LN($B7/Assumptions!$E$7))</f>
         <v>0.502725887222398</v>
       </c>
-      <c r="E7" s="27" t="n">
+      <c r="E7" s="33" t="n">
         <f aca="false">MAX(0.01,Assumptions!$E$10+Assumptions!$E$14*(E$4/Assumptions!$E$5-1)+Assumptions!$E$15*LN($B7/Assumptions!$E$7))</f>
         <v>0.433281442777953</v>
       </c>
-      <c r="F7" s="27" t="n">
+      <c r="F7" s="33" t="n">
         <f aca="false">MAX(0.01,Assumptions!$E$10+Assumptions!$E$14*(F$4/Assumptions!$E$5-1)+Assumptions!$E$15*LN($B7/Assumptions!$E$7))</f>
         <v>0.363836998333509</v>
       </c>
-      <c r="G7" s="27" t="n">
+      <c r="G7" s="33" t="n">
         <f aca="false">MAX(0.01,Assumptions!$E$10+Assumptions!$E$14*(G$4/Assumptions!$E$5-1)+Assumptions!$E$15*LN($B7/Assumptions!$E$7))</f>
         <v>0.294392553889064</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="29" t="n">
+      <c r="B8" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="C8" s="27" t="n">
+      <c r="C8" s="33" t="n">
         <f aca="false">MAX(0.01,Assumptions!$E$10+Assumptions!$E$14*(C$4/Assumptions!$E$5-1)+Assumptions!$E$15*LN($B8/Assumptions!$E$7))</f>
         <v>0.59989621888924</v>
       </c>
-      <c r="D8" s="27" t="n">
+      <c r="D8" s="33" t="n">
         <f aca="false">MAX(0.01,Assumptions!$E$10+Assumptions!$E$14*(D$4/Assumptions!$E$5-1)+Assumptions!$E$15*LN($B8/Assumptions!$E$7))</f>
         <v>0.530451774444796</v>
       </c>
-      <c r="E8" s="27" t="n">
+      <c r="E8" s="33" t="n">
         <f aca="false">MAX(0.01,Assumptions!$E$10+Assumptions!$E$14*(E$4/Assumptions!$E$5-1)+Assumptions!$E$15*LN($B8/Assumptions!$E$7))</f>
         <v>0.461007330000351</v>
       </c>
-      <c r="F8" s="27" t="n">
+      <c r="F8" s="33" t="n">
         <f aca="false">MAX(0.01,Assumptions!$E$10+Assumptions!$E$14*(F$4/Assumptions!$E$5-1)+Assumptions!$E$15*LN($B8/Assumptions!$E$7))</f>
         <v>0.391562885555907</v>
       </c>
-      <c r="G8" s="27" t="n">
+      <c r="G8" s="33" t="n">
         <f aca="false">MAX(0.01,Assumptions!$E$10+Assumptions!$E$14*(G$4/Assumptions!$E$5-1)+Assumptions!$E$15*LN($B8/Assumptions!$E$7))</f>
         <v>0.322118441111462</v>
       </c>
@@ -2712,599 +4756,4 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="B2:M10"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="5" style="1" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="8" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="16"/>
-  </cols>
-  <sheetData>
-    <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="H4" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="I4" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="J4" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="K4" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="L4" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="M4" s="10" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D5" s="30" t="n">
-        <v>10</v>
-      </c>
-      <c r="E5" s="11" t="n">
-        <v>100</v>
-      </c>
-      <c r="F5" s="30" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G5" s="16" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="H5" s="25" t="n">
-        <f aca="false">IF($C5="Call",Assumptions!$E$5*EXP(-Assumptions!$E$9*F5)*NORMSDIST((LN(Assumptions!$E$5/E5)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G5^2)*F5)/(G5*SQRT(F5)))-E5*EXP(-Assumptions!$E$8*F5)*NORMSDIST(((LN(Assumptions!$E$5/E5)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G5^2)*F5)/(G5*SQRT(F5)))-G5*SQRT(F5)),E5*EXP(-Assumptions!$E$8*F5)*NORMSDIST(-(((LN(Assumptions!$E$5/E5)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G5^2)*F5)/(G5*SQRT(F5)))-G5*SQRT(F5)))-Assumptions!$E$5*EXP(-Assumptions!$E$9*F5)*NORMSDIST(-((LN(Assumptions!$E$5/E5)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G5^2)*F5)/(G5*SQRT(F5)))))</f>
-        <v>0.21045244961855</v>
-      </c>
-      <c r="I5" s="1" t="n">
-        <f aca="false">IF($C5="Call",EXP(-Assumptions!$E$9*F5)*NORMSDIST((LN(Assumptions!$E$5/E5)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G5^2)*F5)/(G5*SQRT(F5))),EXP(-Assumptions!$E$9*F5)*(NORMSDIST((LN(Assumptions!$E$5/E5)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G5^2)*F5)/(G5*SQRT(F5)))-1))*D5</f>
-        <v>0.431086690644158</v>
-      </c>
-      <c r="J5" s="1" t="n">
-        <f aca="false">EXP(-Assumptions!$E$9*F5)*(EXP(-(((LN(Assumptions!$E$5/E5)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G5^2)*F5)/(G5*SQRT(F5)))^2)/2)/SQRT(2*PI()))/(Assumptions!$E$5*G5*SQRT(F5))*D5</f>
-        <v>0.0718680647335041</v>
-      </c>
-      <c r="K5" s="1" t="n">
-        <f aca="false">Assumptions!$E$5*EXP(-Assumptions!$E$9*F5)*(EXP(-(((LN(Assumptions!$E$5/E5)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G5^2)*F5)/(G5*SQRT(F5)))^2)/2)/SQRT(2*PI()))*SQRT(F5)*D5</f>
-        <v>46.5705059473107</v>
-      </c>
-      <c r="L5" s="1" t="n">
-        <f aca="false">-Assumptions!$E$5*EXP(-Assumptions!$E$9*F5)*(EXP(-(((LN(Assumptions!$E$5/E5)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G5^2)*F5)/(G5*SQRT(F5)))^2)/2)/SQRT(2*PI()))*G5/(2*SQRT(F5))*D5</f>
-        <v>-11.6426264868277</v>
-      </c>
-      <c r="M5" s="31" t="n">
-        <f aca="false">H5*D5*Assumptions!$E$12</f>
-        <v>210.45244961855</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="D6" s="30" t="n">
-        <v>10</v>
-      </c>
-      <c r="E6" s="11" t="n">
-        <v>90</v>
-      </c>
-      <c r="F6" s="30" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G6" s="16" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H6" s="25" t="n">
-        <f aca="false">IF($C6="Call",Assumptions!$E$5*EXP(-Assumptions!$E$9*F6)*NORMSDIST((LN(Assumptions!$E$5/E6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G6^2)*F6)/(G6*SQRT(F6)))-E6*EXP(-Assumptions!$E$8*F6)*NORMSDIST(((LN(Assumptions!$E$5/E6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G6^2)*F6)/(G6*SQRT(F6)))-G6*SQRT(F6)),E6*EXP(-Assumptions!$E$8*F6)*NORMSDIST(-(((LN(Assumptions!$E$5/E6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G6^2)*F6)/(G6*SQRT(F6)))-G6*SQRT(F6)))-Assumptions!$E$5*EXP(-Assumptions!$E$9*F6)*NORMSDIST(-((LN(Assumptions!$E$5/E6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G6^2)*F6)/(G6*SQRT(F6)))))</f>
-        <v>18.4100145080232</v>
-      </c>
-      <c r="I6" s="1" t="n">
-        <f aca="false">IF($C6="Call",EXP(-Assumptions!$E$9*F6)*NORMSDIST((LN(Assumptions!$E$5/E6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G6^2)*F6)/(G6*SQRT(F6))),EXP(-Assumptions!$E$9*F6)*(NORMSDIST((LN(Assumptions!$E$5/E6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G6^2)*F6)/(G6*SQRT(F6)))-1))*D6</f>
-        <v>-8.11526585455463</v>
-      </c>
-      <c r="J6" s="1" t="n">
-        <f aca="false">EXP(-Assumptions!$E$9*F6)*(EXP(-(((LN(Assumptions!$E$5/E6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G6^2)*F6)/(G6*SQRT(F6)))^2)/2)/SQRT(2*PI()))/(Assumptions!$E$5*G6*SQRT(F6))*D6</f>
-        <v>0.173547126473767</v>
-      </c>
-      <c r="K6" s="1" t="n">
-        <f aca="false">Assumptions!$E$5*EXP(-Assumptions!$E$9*F6)*(EXP(-(((LN(Assumptions!$E$5/E6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G6^2)*F6)/(G6*SQRT(F6)))^2)/2)/SQRT(2*PI()))*SQRT(F6)*D6</f>
-        <v>134.950245546001</v>
-      </c>
-      <c r="L6" s="1" t="n">
-        <f aca="false">-Assumptions!$E$5*EXP(-Assumptions!$E$9*F6)*(EXP(-(((LN(Assumptions!$E$5/E6)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G6^2)*F6)/(G6*SQRT(F6)))^2)/2)/SQRT(2*PI()))*G6/(2*SQRT(F6))*D6</f>
-        <v>-40.4850736638003</v>
-      </c>
-      <c r="M6" s="31" t="n">
-        <f aca="false">H6*D6*Assumptions!$E$12</f>
-        <v>18410.0145080232</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D7" s="30" t="n">
-        <v>-5</v>
-      </c>
-      <c r="E7" s="11" t="n">
-        <v>110</v>
-      </c>
-      <c r="F7" s="30" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G7" s="16" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="H7" s="25" t="n">
-        <f aca="false">IF($C7="Call",Assumptions!$E$5*EXP(-Assumptions!$E$9*F7)*NORMSDIST((LN(Assumptions!$E$5/E7)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G7^2)*F7)/(G7*SQRT(F7)))-E7*EXP(-Assumptions!$E$8*F7)*NORMSDIST(((LN(Assumptions!$E$5/E7)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G7^2)*F7)/(G7*SQRT(F7)))-G7*SQRT(F7)),E7*EXP(-Assumptions!$E$8*F7)*NORMSDIST(-(((LN(Assumptions!$E$5/E7)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G7^2)*F7)/(G7*SQRT(F7)))-G7*SQRT(F7)))-Assumptions!$E$5*EXP(-Assumptions!$E$9*F7)*NORMSDIST(-((LN(Assumptions!$E$5/E7)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G7^2)*F7)/(G7*SQRT(F7)))))</f>
-        <v>0.036099946946677</v>
-      </c>
-      <c r="I7" s="1" t="n">
-        <f aca="false">IF($C7="Call",EXP(-Assumptions!$E$9*F7)*NORMSDIST((LN(Assumptions!$E$5/E7)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G7^2)*F7)/(G7*SQRT(F7))),EXP(-Assumptions!$E$9*F7)*(NORMSDIST((LN(Assumptions!$E$5/E7)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G7^2)*F7)/(G7*SQRT(F7)))-1))*D7</f>
-        <v>-0.0462532932434724</v>
-      </c>
-      <c r="J7" s="1" t="n">
-        <f aca="false">EXP(-Assumptions!$E$9*F7)*(EXP(-(((LN(Assumptions!$E$5/E7)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G7^2)*F7)/(G7*SQRT(F7)))^2)/2)/SQRT(2*PI()))/(Assumptions!$E$5*G7*SQRT(F7))*D7</f>
-        <v>-0.0101820891599</v>
-      </c>
-      <c r="K7" s="1" t="n">
-        <f aca="false">Assumptions!$E$5*EXP(-Assumptions!$E$9*F7)*(EXP(-(((LN(Assumptions!$E$5/E7)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G7^2)*F7)/(G7*SQRT(F7)))^2)/2)/SQRT(2*PI()))*SQRT(F7)*D7</f>
-        <v>-6.33407402459057</v>
-      </c>
-      <c r="L7" s="1" t="n">
-        <f aca="false">-Assumptions!$E$5*EXP(-Assumptions!$E$9*F7)*(EXP(-(((LN(Assumptions!$E$5/E7)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G7^2)*F7)/(G7*SQRT(F7)))^2)/2)/SQRT(2*PI()))*G7/(2*SQRT(F7))*D7</f>
-        <v>1.52017776590174</v>
-      </c>
-      <c r="M7" s="31" t="n">
-        <f aca="false">H7*D7*Assumptions!$E$12</f>
-        <v>-18.0499734733385</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D8" s="30" t="n">
-        <v>4</v>
-      </c>
-      <c r="E8" s="11" t="n">
-        <v>105</v>
-      </c>
-      <c r="F8" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" s="16" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="H8" s="25" t="n">
-        <f aca="false">IF($C8="Call",Assumptions!$E$5*EXP(-Assumptions!$E$9*F8)*NORMSDIST((LN(Assumptions!$E$5/E8)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G8^2)*F8)/(G8*SQRT(F8)))-E8*EXP(-Assumptions!$E$8*F8)*NORMSDIST(((LN(Assumptions!$E$5/E8)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G8^2)*F8)/(G8*SQRT(F8)))-G8*SQRT(F8)),E8*EXP(-Assumptions!$E$8*F8)*NORMSDIST(-(((LN(Assumptions!$E$5/E8)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G8^2)*F8)/(G8*SQRT(F8)))-G8*SQRT(F8)))-Assumptions!$E$5*EXP(-Assumptions!$E$9*F8)*NORMSDIST(-((LN(Assumptions!$E$5/E8)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G8^2)*F8)/(G8*SQRT(F8)))))</f>
-        <v>0.990491653278344</v>
-      </c>
-      <c r="I8" s="1" t="n">
-        <f aca="false">IF($C8="Call",EXP(-Assumptions!$E$9*F8)*NORMSDIST((LN(Assumptions!$E$5/E8)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G8^2)*F8)/(G8*SQRT(F8))),EXP(-Assumptions!$E$9*F8)*(NORMSDIST((LN(Assumptions!$E$5/E8)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G8^2)*F8)/(G8*SQRT(F8)))-1))*D8</f>
-        <v>0.46475023181471</v>
-      </c>
-      <c r="J8" s="1" t="n">
-        <f aca="false">EXP(-Assumptions!$E$9*F8)*(EXP(-(((LN(Assumptions!$E$5/E8)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G8^2)*F8)/(G8*SQRT(F8)))^2)/2)/SQRT(2*PI()))/(Assumptions!$E$5*G8*SQRT(F8))*D8</f>
-        <v>0.0401144108343275</v>
-      </c>
-      <c r="K8" s="1" t="n">
-        <f aca="false">Assumptions!$E$5*EXP(-Assumptions!$E$9*F8)*(EXP(-(((LN(Assumptions!$E$5/E8)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G8^2)*F8)/(G8*SQRT(F8)))^2)/2)/SQRT(2*PI()))*SQRT(F8)*D8</f>
-        <v>56.1473385565915</v>
-      </c>
-      <c r="L8" s="1" t="n">
-        <f aca="false">-Assumptions!$E$5*EXP(-Assumptions!$E$9*F8)*(EXP(-(((LN(Assumptions!$E$5/E8)+(Assumptions!$E$8-Assumptions!$E$9+0.5*G8^2)*F8)/(G8*SQRT(F8)))^2)/2)/SQRT(2*PI()))*G8/(2*SQRT(F8))*D8</f>
-        <v>-7.57989070513985</v>
-      </c>
-      <c r="M8" s="31" t="n">
-        <f aca="false">H8*D8*Assumptions!$E$12</f>
-        <v>396.196661311338</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="32" t="s">
-        <v>108</v>
-      </c>
-      <c r="C10" s="32"/>
-      <c r="D10" s="32"/>
-      <c r="E10" s="32"/>
-      <c r="F10" s="32"/>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="33" t="n">
-        <f aca="false">SUM(I5:I8)</f>
-        <v>-7.26568222533924</v>
-      </c>
-      <c r="J10" s="33" t="n">
-        <f aca="false">SUM(J5:J8)</f>
-        <v>0.275347512881698</v>
-      </c>
-      <c r="K10" s="33" t="n">
-        <f aca="false">SUM(K5:K8)</f>
-        <v>231.334016025313</v>
-      </c>
-      <c r="L10" s="33" t="n">
-        <f aca="false">SUM(L5:L8)</f>
-        <v>-58.1874130898661</v>
-      </c>
-      <c r="M10" s="34" t="n">
-        <f aca="false">SUM(M5:M8)</f>
-        <v>18998.6136454798</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B2:M2"/>
-  </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="B2:H9"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="1" width="14"/>
-  </cols>
-  <sheetData>
-    <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="C4" s="35" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="D4" s="35" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="E4" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="35" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G4" s="35" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="36" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="C5" s="31" t="n">
-        <f aca="false">Portfolio!$I$10*(Assumptions!$E$5*$B5)+0.5*Portfolio!$J$10*(Assumptions!$E$5*$B5)^2+Portfolio!$K$10*C$4</f>
-        <v>110.040452577928</v>
-      </c>
-      <c r="D5" s="31" t="n">
-        <f aca="false">Portfolio!$I$10*(Assumptions!$E$5*$B5)+0.5*Portfolio!$J$10*(Assumptions!$E$5*$B5)^2+Portfolio!$K$10*D$4</f>
-        <v>121.607153379194</v>
-      </c>
-      <c r="E5" s="31" t="n">
-        <f aca="false">Portfolio!$I$10*(Assumptions!$E$5*$B5)+0.5*Portfolio!$J$10*(Assumptions!$E$5*$B5)^2+Portfolio!$K$10*E$4</f>
-        <v>133.17385418046</v>
-      </c>
-      <c r="F5" s="31" t="n">
-        <f aca="false">Portfolio!$I$10*(Assumptions!$E$5*$B5)+0.5*Portfolio!$J$10*(Assumptions!$E$5*$B5)^2+Portfolio!$K$10*F$4</f>
-        <v>144.740554981725</v>
-      </c>
-      <c r="G5" s="31" t="n">
-        <f aca="false">Portfolio!$I$10*(Assumptions!$E$5*$B5)+0.5*Portfolio!$J$10*(Assumptions!$E$5*$B5)^2+Portfolio!$K$10*G$4</f>
-        <v>156.307255782991</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="36" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="C6" s="31" t="n">
-        <f aca="false">Portfolio!$I$10*(Assumptions!$E$5*$B6)+0.5*Portfolio!$J$10*(Assumptions!$E$5*$B6)^2+Portfolio!$K$10*C$4</f>
-        <v>36.3165179538049</v>
-      </c>
-      <c r="D6" s="31" t="n">
-        <f aca="false">Portfolio!$I$10*(Assumptions!$E$5*$B6)+0.5*Portfolio!$J$10*(Assumptions!$E$5*$B6)^2+Portfolio!$K$10*D$4</f>
-        <v>47.8832187550705</v>
-      </c>
-      <c r="E6" s="31" t="n">
-        <f aca="false">Portfolio!$I$10*(Assumptions!$E$5*$B6)+0.5*Portfolio!$J$10*(Assumptions!$E$5*$B6)^2+Portfolio!$K$10*E$4</f>
-        <v>59.4499195563361</v>
-      </c>
-      <c r="F6" s="31" t="n">
-        <f aca="false">Portfolio!$I$10*(Assumptions!$E$5*$B6)+0.5*Portfolio!$J$10*(Assumptions!$E$5*$B6)^2+Portfolio!$K$10*F$4</f>
-        <v>71.0166203576018</v>
-      </c>
-      <c r="G6" s="31" t="n">
-        <f aca="false">Portfolio!$I$10*(Assumptions!$E$5*$B6)+0.5*Portfolio!$J$10*(Assumptions!$E$5*$B6)^2+Portfolio!$K$10*G$4</f>
-        <v>82.5833211588674</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="31" t="n">
-        <f aca="false">Portfolio!$I$10*(Assumptions!$E$5*$B7)+0.5*Portfolio!$J$10*(Assumptions!$E$5*$B7)^2+Portfolio!$K$10*C$4</f>
-        <v>-23.1334016025313</v>
-      </c>
-      <c r="D7" s="31" t="n">
-        <f aca="false">Portfolio!$I$10*(Assumptions!$E$5*$B7)+0.5*Portfolio!$J$10*(Assumptions!$E$5*$B7)^2+Portfolio!$K$10*D$4</f>
-        <v>-11.5667008012656</v>
-      </c>
-      <c r="E7" s="31" t="n">
-        <f aca="false">Portfolio!$I$10*(Assumptions!$E$5*$B7)+0.5*Portfolio!$J$10*(Assumptions!$E$5*$B7)^2+Portfolio!$K$10*E$4</f>
-        <v>0</v>
-      </c>
-      <c r="F7" s="31" t="n">
-        <f aca="false">Portfolio!$I$10*(Assumptions!$E$5*$B7)+0.5*Portfolio!$J$10*(Assumptions!$E$5*$B7)^2+Portfolio!$K$10*F$4</f>
-        <v>11.5667008012656</v>
-      </c>
-      <c r="G7" s="31" t="n">
-        <f aca="false">Portfolio!$I$10*(Assumptions!$E$5*$B7)+0.5*Portfolio!$J$10*(Assumptions!$E$5*$B7)^2+Portfolio!$K$10*G$4</f>
-        <v>23.1334016025313</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="36" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C8" s="31" t="n">
-        <f aca="false">Portfolio!$I$10*(Assumptions!$E$5*$B8)+0.5*Portfolio!$J$10*(Assumptions!$E$5*$B8)^2+Portfolio!$K$10*C$4</f>
-        <v>-68.3093060910802</v>
-      </c>
-      <c r="D8" s="31" t="n">
-        <f aca="false">Portfolio!$I$10*(Assumptions!$E$5*$B8)+0.5*Portfolio!$J$10*(Assumptions!$E$5*$B8)^2+Portfolio!$K$10*D$4</f>
-        <v>-56.7426052898145</v>
-      </c>
-      <c r="E8" s="31" t="n">
-        <f aca="false">Portfolio!$I$10*(Assumptions!$E$5*$B8)+0.5*Portfolio!$J$10*(Assumptions!$E$5*$B8)^2+Portfolio!$K$10*E$4</f>
-        <v>-45.1759044885489</v>
-      </c>
-      <c r="F8" s="31" t="n">
-        <f aca="false">Portfolio!$I$10*(Assumptions!$E$5*$B8)+0.5*Portfolio!$J$10*(Assumptions!$E$5*$B8)^2+Portfolio!$K$10*F$4</f>
-        <v>-33.6092036872833</v>
-      </c>
-      <c r="G8" s="31" t="n">
-        <f aca="false">Portfolio!$I$10*(Assumptions!$E$5*$B8)+0.5*Portfolio!$J$10*(Assumptions!$E$5*$B8)^2+Portfolio!$K$10*G$4</f>
-        <v>-22.0425028860176</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="36" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="C9" s="31" t="n">
-        <f aca="false">Portfolio!$I$10*(Assumptions!$E$5*$B9)+0.5*Portfolio!$J$10*(Assumptions!$E$5*$B9)^2+Portfolio!$K$10*C$4</f>
-        <v>-99.2111955118418</v>
-      </c>
-      <c r="D9" s="31" t="n">
-        <f aca="false">Portfolio!$I$10*(Assumptions!$E$5*$B9)+0.5*Portfolio!$J$10*(Assumptions!$E$5*$B9)^2+Portfolio!$K$10*D$4</f>
-        <v>-87.6444947105762</v>
-      </c>
-      <c r="E9" s="31" t="n">
-        <f aca="false">Portfolio!$I$10*(Assumptions!$E$5*$B9)+0.5*Portfolio!$J$10*(Assumptions!$E$5*$B9)^2+Portfolio!$K$10*E$4</f>
-        <v>-76.0777939093105</v>
-      </c>
-      <c r="F9" s="31" t="n">
-        <f aca="false">Portfolio!$I$10*(Assumptions!$E$5*$B9)+0.5*Portfolio!$J$10*(Assumptions!$E$5*$B9)^2+Portfolio!$K$10*F$4</f>
-        <v>-64.5110931080449</v>
-      </c>
-      <c r="G9" s="31" t="n">
-        <f aca="false">Portfolio!$I$10*(Assumptions!$E$5*$B9)+0.5*Portfolio!$J$10*(Assumptions!$E$5*$B9)^2+Portfolio!$K$10*G$4</f>
-        <v>-52.9443923067793</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B2:H2"/>
-  </mergeCells>
-  <conditionalFormatting sqref="C5:G9">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFFCE4D6"/>
-        <color rgb="FFFFF2CC"/>
-        <color rgb="FFE2F0D9"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="B2:C10"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18"/>
-  </cols>
-  <sheetData>
-    <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C2" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="C5" s="1" t="str">
-        <f aca="false">IF(ABS('European Pricer'!C13)&lt;0.000001,"PASS","FAIL")</f>
-        <v>PASS</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="C6" s="1" t="str">
-        <f aca="false">IF('Implied Vol'!E17&lt;0.0001,"PASS","REVIEW")</f>
-        <v>REVIEW</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="C7" s="1" t="str">
-        <f aca="false">IF(AND(Greeks!C6&gt;0,Greeks!D6&gt;0),"PASS","FAIL")</f>
-        <v>PASS</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="C8" s="1" t="str">
-        <f aca="false">IF(AND('European Pricer'!C7&gt;=MAX(0,Assumptions!E5*EXP(-Assumptions!E9*Assumptions!E7)-Assumptions!E6*EXP(-Assumptions!E8*Assumptions!E7)),'European Pricer'!C7&lt;=Assumptions!E5*EXP(-Assumptions!E9*Assumptions!E7)),"PASS","FAIL")</f>
-        <v>PASS</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="C9" s="1" t="str">
-        <f aca="false">IF(COUNT(Portfolio!H5:M8)=24,"PASS","FAIL")</f>
-        <v>PASS</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C10" s="1" t="str">
-        <f aca="false">IF(COUNTIF(C5:C9,"FAIL")=0,"PASS","FAIL")</f>
-        <v>PASS</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B2:C2"/>
-  </mergeCells>
-  <conditionalFormatting sqref="C5:C10">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>C5="PASS"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
-      <formula>C5="FAIL"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
-      <formula>C5="REVIEW"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
-      <formula>C5="BREACH"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
 </file>